--- a/data/kearney18_s1_figuredata.xlsx
+++ b/data/kearney18_s1_figuredata.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="28615"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kearney conor/kearney conor/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aacc6cdd8e068f2a/Documents/Cheng-Lab/Coculture-Project/invitro-crispr-tnfsensitivity-science2018-replication/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_79E4B54BF3F0DA831B5625346E7236F008263A7E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3500" yWindow="1660" windowWidth="28800" windowHeight="15700" tabRatio="500" activeTab="5"/>
+    <workbookView minimized="1" xWindow="20160" yWindow="-14550" windowWidth="21600" windowHeight="11175" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Figure 1B" sheetId="4" r:id="rId1"/>
@@ -1149,7 +1150,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -1354,7 +1355,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1364,16 +1365,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1384,7 +1381,6 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1394,10 +1390,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1485,6 +1480,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1752,20 +1750,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>38</v>
       </c>
@@ -1773,7 +1771,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>0.72538860000000005</v>
       </c>
@@ -1781,7 +1779,7 @@
         <v>1.226</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>1.3989640000000001</v>
       </c>
@@ -1789,7 +1787,7 @@
         <v>2.1659999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>0.88082899999999997</v>
       </c>
@@ -1797,22 +1795,22 @@
         <v>2.4900000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>36</v>
       </c>
@@ -1820,7 +1818,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>168.75</v>
       </c>
@@ -1828,7 +1826,7 @@
         <v>227.68</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>153.80000000000001</v>
       </c>
@@ -1836,7 +1834,7 @@
         <v>235.02</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>135.16999999999999</v>
       </c>
@@ -1844,12 +1842,12 @@
         <v>198.13</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
         <v>12</v>
       </c>
@@ -1860,15 +1858,15 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.83203125" customWidth="1"/>
     <col min="2" max="2" width="17.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>84</v>
       </c>
@@ -1882,7 +1880,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>96.547619049999994</v>
       </c>
@@ -1896,7 +1894,7 @@
         <v>42.559523810000002</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>99.591836729999997</v>
       </c>
@@ -1910,7 +1908,7 @@
         <v>54.693877550000003</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>95.890410959999997</v>
       </c>
@@ -1924,7 +1922,7 @@
         <v>63.01369863</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C6" t="s">
         <v>85</v>
       </c>
@@ -1932,7 +1930,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C7" t="s">
         <v>12</v>
       </c>
@@ -1946,15 +1944,15 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
     <col min="2" max="2" width="18.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>78</v>
       </c>
@@ -1968,7 +1966,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>53.6</v>
       </c>
@@ -1982,7 +1980,7 @@
         <v>56.36</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>168.78</v>
       </c>
@@ -1996,7 +1994,7 @@
         <v>129.47999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>75.22</v>
       </c>
@@ -2010,7 +2008,7 @@
         <v>89.42</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C5" t="s">
         <v>88</v>
       </c>
@@ -2024,9 +2022,9 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.33203125" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -2034,7 +2032,7 @@
     <col min="4" max="4" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>89</v>
       </c>
@@ -2048,7 +2046,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>98.167006110000003</v>
       </c>
@@ -2062,7 +2060,7 @@
         <v>38.832315000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>98.167006110000003</v>
       </c>
@@ -2076,7 +2074,7 @@
         <v>57.725947519999998</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>98.167006110000003</v>
       </c>
@@ -2090,7 +2088,7 @@
         <v>46.347941570000003</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C6" t="s">
         <v>2</v>
       </c>
@@ -2104,9 +2102,9 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.33203125" customWidth="1"/>
     <col min="2" max="2" width="17.33203125" customWidth="1"/>
@@ -2114,7 +2112,7 @@
     <col min="4" max="4" width="21.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>78</v>
       </c>
@@ -2128,7 +2126,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>100.178731</v>
       </c>
@@ -2142,7 +2140,7 @@
         <v>83.109919570000002</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>92.897907419999996</v>
       </c>
@@ -2156,7 +2154,7 @@
         <v>61.160431199999998</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>104</v>
       </c>
@@ -2170,7 +2168,7 @@
         <v>71.777777779999994</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C6" t="s">
         <v>91</v>
       </c>
@@ -2184,15 +2182,15 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
     <col min="2" max="2" width="15.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>16</v>
       </c>
@@ -2206,7 +2204,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>100</v>
       </c>
@@ -2220,7 +2218,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>100</v>
       </c>
@@ -2234,7 +2232,7 @@
         <v>33.96</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>100</v>
       </c>
@@ -2248,7 +2246,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>11</v>
       </c>
@@ -2259,7 +2257,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C7" t="s">
         <v>12</v>
       </c>
@@ -2273,9 +2271,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21.33203125" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -2291,7 +2289,7 @@
     <col min="14" max="14" width="13.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2335,7 +2333,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>100</v>
       </c>
@@ -2379,7 +2377,7 @@
         <v>75.471698110000005</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>100</v>
       </c>
@@ -2423,7 +2421,7 @@
         <v>74.526928679999997</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>100</v>
       </c>
@@ -2467,7 +2465,7 @@
         <v>124.537037</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
         <v>11</v>
       </c>
@@ -2508,7 +2506,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="C8" t="s">
         <v>12</v>
       </c>
@@ -2546,9 +2544,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:P66"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.5" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
@@ -2558,12 +2556,12 @@
     <col min="13" max="13" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="C4" s="3" t="s">
         <v>42</v>
       </c>
@@ -2583,7 +2581,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="O5">
         <v>80</v>
       </c>
@@ -2591,14 +2589,14 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="C6" s="4">
         <v>1</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" t="s">
         <v>47</v>
       </c>
       <c r="G6" s="4">
@@ -2607,7 +2605,7 @@
       <c r="H6" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" t="s">
         <v>48</v>
       </c>
       <c r="M6" s="3"/>
@@ -2618,14 +2616,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="C7" s="4">
         <v>2</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" t="s">
         <v>47</v>
       </c>
       <c r="G7" s="4">
@@ -2634,7 +2632,7 @@
       <c r="H7" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="I7" t="s">
         <v>48</v>
       </c>
       <c r="O7">
@@ -2644,14 +2642,14 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="C8" s="4">
         <v>3</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" t="s">
         <v>47</v>
       </c>
       <c r="G8" s="4">
@@ -2660,18 +2658,18 @@
       <c r="H8" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="I8" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="C9" s="4">
         <v>4</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" t="s">
         <v>47</v>
       </c>
       <c r="G9" s="4">
@@ -2680,7 +2678,7 @@
       <c r="H9" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" t="s">
         <v>48</v>
       </c>
       <c r="M9" s="3" t="s">
@@ -2690,14 +2688,14 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="C10" s="4">
         <v>5</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" t="s">
         <v>47</v>
       </c>
       <c r="G10" s="4">
@@ -2706,21 +2704,21 @@
       <c r="H10" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" t="s">
         <v>48</v>
       </c>
       <c r="P10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="C11" s="4">
         <v>6</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" t="s">
         <v>47</v>
       </c>
       <c r="G11" s="4">
@@ -2729,18 +2727,18 @@
       <c r="H11" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="I11" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="C12" s="4">
         <v>7</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" t="s">
         <v>47</v>
       </c>
       <c r="G12" s="4">
@@ -2749,18 +2747,18 @@
       <c r="H12" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="I12" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="C13" s="4">
         <v>8</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" t="s">
         <v>47</v>
       </c>
       <c r="G13" s="4">
@@ -2769,18 +2767,18 @@
       <c r="H13" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="I13" s="6" t="s">
+      <c r="I13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="C14" s="4">
         <v>9</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" t="s">
         <v>47</v>
       </c>
       <c r="G14" s="4">
@@ -2789,18 +2787,18 @@
       <c r="H14" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="I14" s="6" t="s">
+      <c r="I14" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="C15" s="7">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="C15" s="6">
         <v>10</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" t="s">
         <v>47</v>
       </c>
       <c r="G15" s="4">
@@ -2809,18 +2807,18 @@
       <c r="H15" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="I15" s="6" t="s">
+      <c r="I15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="C16" s="4">
         <v>11</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" t="s">
         <v>47</v>
       </c>
       <c r="G16" s="4">
@@ -2829,38 +2827,38 @@
       <c r="H16" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="I16" s="6" t="s">
+      <c r="I16" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="C17" s="9" t="s">
+    <row r="17" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C17" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" t="s">
         <v>47</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G17" s="6">
         <v>12</v>
       </c>
-      <c r="H17" s="8" t="s">
+      <c r="H17" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="I17" s="6" t="s">
+      <c r="I17" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="C18" s="9">
+    <row r="18" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C18" s="4">
         <v>13</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" t="s">
         <v>47</v>
       </c>
       <c r="G18" s="4">
@@ -2869,146 +2867,146 @@
       <c r="H18" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="I18" s="6" t="s">
+      <c r="I18" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="C19" s="9">
+    <row r="19" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C19" s="4">
         <v>14</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" t="s">
         <v>47</v>
       </c>
-      <c r="G19" s="9">
+      <c r="G19" s="4">
         <v>14</v>
       </c>
-      <c r="H19" s="10" t="s">
+      <c r="H19" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="I19" s="6" t="s">
+      <c r="I19" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="C20" s="9">
+    <row r="20" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C20" s="4">
         <v>15</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" t="s">
         <v>47</v>
       </c>
-      <c r="G20" s="9">
+      <c r="G20" s="4">
         <v>15</v>
       </c>
-      <c r="H20" s="10" t="s">
+      <c r="H20" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="I20" s="6" t="s">
+      <c r="I20" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="C21" s="7">
+    <row r="21" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C21" s="6">
         <v>16</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" t="s">
         <v>47</v>
       </c>
-      <c r="G21" s="7">
+      <c r="G21" s="6">
         <v>16</v>
       </c>
-      <c r="H21" s="8" t="s">
+      <c r="H21" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="I21" s="6" t="s">
+      <c r="I21" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="22" spans="3:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C22" s="7">
+    <row r="22" spans="3:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C22" s="6">
         <v>17</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" t="s">
         <v>47</v>
       </c>
-      <c r="G22" s="11">
+      <c r="G22" s="9">
         <v>1</v>
       </c>
-      <c r="H22" s="12" t="s">
+      <c r="H22" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="I22" s="6" t="s">
+      <c r="I22" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="C23" s="9">
+    <row r="23" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C23" s="4">
         <v>18</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E23" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="C24" s="7">
+    <row r="24" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C24" s="6">
         <v>19</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="E24" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="C25" s="9">
+    <row r="25" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C25" s="4">
         <v>20</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E25" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="26" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="C26" s="7">
+    <row r="26" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C26" s="6">
         <v>21</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D26" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="E26" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="3:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C27" s="13">
+    <row r="27" spans="3:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C27" s="11">
         <v>22</v>
       </c>
-      <c r="D27" s="14" t="s">
+      <c r="D27" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="3:9" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C30" s="3" t="s">
         <v>54</v>
       </c>
@@ -3016,7 +3014,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="32" spans="3:9" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C32">
         <v>1</v>
       </c>
@@ -3026,17 +3024,17 @@
       <c r="E32" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="15">
+      <c r="G32" s="13">
         <v>1</v>
       </c>
-      <c r="H32" s="6" t="s">
+      <c r="H32" t="s">
         <v>56</v>
       </c>
-      <c r="I32" s="6" t="s">
+      <c r="I32" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="33" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C33">
         <v>2</v>
       </c>
@@ -3046,17 +3044,17 @@
       <c r="E33" t="s">
         <v>57</v>
       </c>
-      <c r="G33" s="15">
+      <c r="G33" s="13">
         <v>2</v>
       </c>
-      <c r="H33" s="6" t="s">
+      <c r="H33" t="s">
         <v>56</v>
       </c>
-      <c r="I33" s="6" t="s">
+      <c r="I33" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="34" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C34">
         <v>3</v>
       </c>
@@ -3066,17 +3064,17 @@
       <c r="E34" t="s">
         <v>57</v>
       </c>
-      <c r="G34" s="15">
+      <c r="G34" s="13">
         <v>3</v>
       </c>
-      <c r="H34" s="6" t="s">
+      <c r="H34" t="s">
         <v>56</v>
       </c>
-      <c r="I34" s="6" t="s">
+      <c r="I34" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="35" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="35" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C35">
         <v>4</v>
       </c>
@@ -3086,17 +3084,17 @@
       <c r="E35" t="s">
         <v>57</v>
       </c>
-      <c r="G35" s="15">
+      <c r="G35" s="13">
         <v>4</v>
       </c>
-      <c r="H35" s="6" t="s">
+      <c r="H35" t="s">
         <v>56</v>
       </c>
-      <c r="I35" s="6" t="s">
+      <c r="I35" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="36" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="36" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C36">
         <v>5</v>
       </c>
@@ -3106,17 +3104,17 @@
       <c r="E36" t="s">
         <v>57</v>
       </c>
-      <c r="G36" s="15">
+      <c r="G36" s="13">
         <v>5</v>
       </c>
-      <c r="H36" s="6" t="s">
+      <c r="H36" t="s">
         <v>56</v>
       </c>
-      <c r="I36" s="6" t="s">
+      <c r="I36" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="37" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C37">
         <v>6</v>
       </c>
@@ -3126,17 +3124,17 @@
       <c r="E37" t="s">
         <v>57</v>
       </c>
-      <c r="G37" s="15">
+      <c r="G37" s="13">
         <v>6</v>
       </c>
-      <c r="H37" s="6" t="s">
+      <c r="H37" t="s">
         <v>56</v>
       </c>
-      <c r="I37" s="6" t="s">
+      <c r="I37" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="38" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C38">
         <v>7</v>
       </c>
@@ -3146,17 +3144,17 @@
       <c r="E38" t="s">
         <v>57</v>
       </c>
-      <c r="G38" s="15">
+      <c r="G38" s="13">
         <v>7</v>
       </c>
-      <c r="H38" s="6" t="s">
+      <c r="H38" t="s">
         <v>56</v>
       </c>
-      <c r="I38" s="6" t="s">
+      <c r="I38" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="39" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C39">
         <v>8</v>
       </c>
@@ -3166,17 +3164,17 @@
       <c r="E39" t="s">
         <v>57</v>
       </c>
-      <c r="G39" s="15">
+      <c r="G39" s="13">
         <v>8</v>
       </c>
-      <c r="H39" s="6" t="s">
+      <c r="H39" t="s">
         <v>56</v>
       </c>
-      <c r="I39" s="6" t="s">
+      <c r="I39" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="40" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="40" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C40">
         <v>9</v>
       </c>
@@ -3186,20 +3184,20 @@
       <c r="E40" t="s">
         <v>57</v>
       </c>
-      <c r="G40" s="15">
+      <c r="G40" s="13">
         <v>9</v>
       </c>
-      <c r="H40" s="6" t="s">
+      <c r="H40" t="s">
         <v>56</v>
       </c>
-      <c r="I40" s="6" t="s">
+      <c r="I40" t="s">
         <v>57</v>
       </c>
       <c r="M40" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="41" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="41" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C41">
         <v>10</v>
       </c>
@@ -3209,17 +3207,17 @@
       <c r="E41" t="s">
         <v>57</v>
       </c>
-      <c r="G41" s="15">
+      <c r="G41" s="13">
         <v>10</v>
       </c>
-      <c r="H41" s="6" t="s">
+      <c r="H41" t="s">
         <v>56</v>
       </c>
-      <c r="I41" s="6" t="s">
+      <c r="I41" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="42" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C42">
         <v>11</v>
       </c>
@@ -3229,17 +3227,17 @@
       <c r="E42" t="s">
         <v>57</v>
       </c>
-      <c r="G42" s="15">
+      <c r="G42" s="13">
         <v>11</v>
       </c>
-      <c r="H42" s="6" t="s">
+      <c r="H42" t="s">
         <v>56</v>
       </c>
-      <c r="I42" s="6" t="s">
+      <c r="I42" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="43" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C43">
         <v>12</v>
       </c>
@@ -3249,17 +3247,17 @@
       <c r="E43" t="s">
         <v>57</v>
       </c>
-      <c r="G43" s="15">
+      <c r="G43" s="13">
         <v>12</v>
       </c>
-      <c r="H43" s="6" t="s">
+      <c r="H43" t="s">
         <v>56</v>
       </c>
-      <c r="I43" s="6" t="s">
+      <c r="I43" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="44" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C44">
         <v>13</v>
       </c>
@@ -3269,296 +3267,296 @@
       <c r="E44" t="s">
         <v>57</v>
       </c>
-      <c r="G44" s="15">
+      <c r="G44" s="13">
         <v>13</v>
       </c>
-      <c r="H44" s="6" t="s">
+      <c r="H44" t="s">
         <v>56</v>
       </c>
-      <c r="I44" s="6" t="s">
+      <c r="I44" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="45" spans="3:13" x14ac:dyDescent="0.2">
-      <c r="C45" s="16">
+    <row r="45" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C45" s="14">
         <v>14</v>
       </c>
-      <c r="D45" s="16" t="s">
+      <c r="D45" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="E45" s="16" t="s">
+      <c r="E45" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="G45" s="15">
+      <c r="G45" s="13">
         <v>14</v>
       </c>
-      <c r="H45" s="6" t="s">
+      <c r="H45" t="s">
         <v>56</v>
       </c>
-      <c r="I45" s="6" t="s">
+      <c r="I45" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="46" spans="3:13" x14ac:dyDescent="0.2">
-      <c r="C46" s="16">
+    <row r="46" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C46" s="14">
         <v>15</v>
       </c>
-      <c r="D46" s="16" t="s">
+      <c r="D46" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="E46" s="16" t="s">
+      <c r="E46" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="G46" s="15">
+      <c r="G46" s="13">
         <v>15</v>
       </c>
-      <c r="H46" s="6" t="s">
+      <c r="H46" t="s">
         <v>56</v>
       </c>
-      <c r="I46" s="6" t="s">
+      <c r="I46" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="47" spans="3:13" x14ac:dyDescent="0.2">
-      <c r="C47" s="16">
+    <row r="47" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C47" s="14">
         <v>16</v>
       </c>
-      <c r="D47" s="16" t="s">
+      <c r="D47" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="E47" s="16" t="s">
+      <c r="E47" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="G47" s="15">
+      <c r="G47" s="13">
         <v>16</v>
       </c>
-      <c r="H47" s="6" t="s">
+      <c r="H47" t="s">
         <v>56</v>
       </c>
-      <c r="I47" s="6" t="s">
+      <c r="I47" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="3:13" x14ac:dyDescent="0.2">
-      <c r="C48" s="16">
+    <row r="48" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C48" s="14">
         <v>17</v>
       </c>
-      <c r="D48" s="16" t="s">
+      <c r="D48" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="E48" s="16" t="s">
+      <c r="E48" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="G48" s="15">
+      <c r="G48" s="13">
         <v>17</v>
       </c>
-      <c r="H48" s="6" t="s">
+      <c r="H48" t="s">
         <v>56</v>
       </c>
-      <c r="I48" s="6" t="s">
+      <c r="I48" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
-      <c r="C49" s="17">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C49">
         <v>18</v>
       </c>
-      <c r="D49" s="17" t="s">
+      <c r="D49" t="s">
         <v>56</v>
       </c>
-      <c r="E49" s="17" t="s">
+      <c r="E49" t="s">
         <v>57</v>
       </c>
-      <c r="G49" s="15">
+      <c r="G49" s="13">
         <v>18</v>
       </c>
-      <c r="H49" s="6" t="s">
+      <c r="H49" t="s">
         <v>56</v>
       </c>
-      <c r="I49" s="6" t="s">
+      <c r="I49" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
-      <c r="C50" s="16">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C50" s="14">
         <v>19</v>
       </c>
-      <c r="D50" s="16" t="s">
+      <c r="D50" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="E50" s="16" t="s">
+      <c r="E50" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="G50" s="15">
+      <c r="G50" s="13">
         <v>19</v>
       </c>
-      <c r="H50" s="6" t="s">
+      <c r="H50" t="s">
         <v>56</v>
       </c>
-      <c r="I50" s="6" t="s">
+      <c r="I50" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
-      <c r="C51" s="16">
+    <row r="51" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C51" s="14">
         <v>20</v>
       </c>
-      <c r="D51" s="16" t="s">
+      <c r="D51" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="E51" s="16" t="s">
+      <c r="E51" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="G51" s="15">
+      <c r="G51" s="13">
         <v>20</v>
       </c>
-      <c r="H51" s="6" t="s">
+      <c r="H51" t="s">
         <v>56</v>
       </c>
-      <c r="I51" s="6" t="s">
+      <c r="I51" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
-      <c r="G52" s="15">
+    <row r="52" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="G52" s="13">
         <v>21</v>
       </c>
-      <c r="H52" s="6" t="s">
+      <c r="H52" t="s">
         <v>56</v>
       </c>
-      <c r="I52" s="6" t="s">
+      <c r="I52" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="3:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="G53" s="18">
+    <row r="53" spans="3:13" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G53" s="15">
         <v>22</v>
       </c>
-      <c r="H53" s="19" t="s">
+      <c r="H53" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="I53" s="19" t="s">
+      <c r="I53" s="16" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C58" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
-      <c r="C60" s="16">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C60" s="14">
         <v>1</v>
       </c>
-      <c r="D60" s="16" t="s">
+      <c r="D60" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="E60" s="16" t="s">
+      <c r="E60" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="G60" s="16">
+      <c r="G60" s="14">
         <v>1</v>
       </c>
-      <c r="H60" s="16" t="s">
+      <c r="H60" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="I60" s="16" t="s">
+      <c r="I60" s="14" t="s">
         <v>57</v>
       </c>
       <c r="M60" s="3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
-      <c r="C61" s="16">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C61" s="14">
         <v>2</v>
       </c>
-      <c r="D61" s="16" t="s">
+      <c r="D61" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="E61" s="16" t="s">
+      <c r="E61" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="G61" s="16">
+      <c r="G61" s="14">
         <v>2</v>
       </c>
-      <c r="H61" s="16" t="s">
+      <c r="H61" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="I61" s="16" t="s">
+      <c r="I61" s="14" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
-      <c r="C62" s="16">
+    <row r="62" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C62" s="14">
         <v>3</v>
       </c>
-      <c r="D62" s="16" t="s">
+      <c r="D62" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="E62" s="16" t="s">
+      <c r="E62" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="G62" s="20" t="s">
+      <c r="G62" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="H62" s="20" t="s">
+      <c r="H62" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="I62" s="20" t="s">
+      <c r="I62" s="17" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
-      <c r="C63" s="16">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C63" s="14">
         <v>4</v>
       </c>
-      <c r="D63" s="16" t="s">
+      <c r="D63" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="E63" s="16" t="s">
+      <c r="E63" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="G63" s="16">
+      <c r="G63" s="14">
         <v>1</v>
       </c>
-      <c r="H63" s="16" t="s">
+      <c r="H63" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="I63" s="16" t="s">
+      <c r="I63" s="14" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
-      <c r="C64" s="16">
+    <row r="64" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C64" s="14">
         <v>5</v>
       </c>
-      <c r="D64" s="16" t="s">
+      <c r="D64" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="E64" s="16" t="s">
+      <c r="E64" s="14" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="65" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C65" s="16">
+    <row r="65" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C65" s="14">
         <v>6</v>
       </c>
-      <c r="D65" s="16" t="s">
+      <c r="D65" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="E65" s="16" t="s">
+      <c r="E65" s="14" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="66" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C66" s="16">
+    <row r="66" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C66" s="14">
         <v>7</v>
       </c>
-      <c r="D66" s="16" t="s">
+      <c r="D66" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="E66" s="16" t="s">
+      <c r="E66" s="14" t="s">
         <v>57</v>
       </c>
     </row>
@@ -3568,24 +3566,24 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:Y17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A2" s="23" t="s">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
         <v>94</v>
       </c>
@@ -3648,39 +3646,39 @@
         <v>103</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="27"/>
-      <c r="K4" s="27"/>
-      <c r="L4" s="27"/>
-      <c r="M4" s="27" t="s">
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="N4" s="28"/>
-      <c r="O4" s="28"/>
-      <c r="P4" s="28"/>
-      <c r="Q4" s="28"/>
-      <c r="R4" s="28"/>
-      <c r="S4" s="28"/>
-      <c r="T4" s="28"/>
-      <c r="U4" s="28"/>
-      <c r="V4" s="28"/>
-      <c r="W4" s="28"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="24"/>
+      <c r="Q4" s="24"/>
+      <c r="R4" s="24"/>
+      <c r="S4" s="24"/>
+      <c r="T4" s="24"/>
+      <c r="U4" s="24"/>
+      <c r="V4" s="24"/>
+      <c r="W4" s="24"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A5" s="24">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A5" s="20">
         <v>0</v>
       </c>
       <c r="B5" s="1">
@@ -3749,8 +3747,8 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A6" s="24">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A6" s="20">
         <v>7</v>
       </c>
       <c r="B6" s="1">
@@ -3819,8 +3817,8 @@
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A7" s="24">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A7" s="20">
         <v>9</v>
       </c>
       <c r="B7" s="1">
@@ -3889,8 +3887,8 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A8" s="24">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A8" s="20">
         <v>12</v>
       </c>
       <c r="B8" s="1">
@@ -3959,8 +3957,8 @@
         <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A9" s="24">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A9" s="20">
         <v>14</v>
       </c>
       <c r="B9" s="1">
@@ -4029,8 +4027,8 @@
         <v>88</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A10" s="24">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A10" s="20">
         <v>16</v>
       </c>
       <c r="B10" s="1">
@@ -4099,8 +4097,8 @@
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A11" s="24">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A11" s="20">
         <v>19</v>
       </c>
       <c r="B11" s="1">
@@ -4172,8 +4170,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A12" s="24">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A12" s="20">
         <v>21</v>
       </c>
       <c r="B12" s="1">
@@ -4245,8 +4243,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A13" s="24">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A13" s="20">
         <v>23</v>
       </c>
       <c r="B13" s="1">
@@ -4318,8 +4316,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A14" s="24">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A14" s="20">
         <v>26</v>
       </c>
       <c r="B14" s="1">
@@ -4391,8 +4389,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A15" s="24">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A15" s="20">
         <v>28</v>
       </c>
       <c r="B15" s="1">
@@ -4464,8 +4462,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A16" s="24">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A16" s="20">
         <v>30</v>
       </c>
       <c r="B16" s="1">
@@ -4537,8 +4535,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A17" s="24">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A17" s="20">
         <v>33</v>
       </c>
       <c r="B17" s="1">
@@ -4620,11 +4618,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>67</v>
       </c>
@@ -4638,7 +4636,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>54.432299999999998</v>
       </c>
@@ -4652,7 +4650,7 @@
         <v>120.15600000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>74.760000000000005</v>
       </c>
@@ -4666,7 +4664,7 @@
         <v>101.535</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>28.924800000000001</v>
       </c>
@@ -4680,7 +4678,7 @@
         <v>104.9025</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>38.04</v>
       </c>
@@ -4694,7 +4692,7 @@
         <v>108.15</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>46.808999999999997</v>
       </c>
@@ -4708,7 +4706,7 @@
         <v>116.235</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>67.830699999999993</v>
       </c>
@@ -4722,7 +4720,7 @@
         <v>115.9344</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>2</v>
       </c>
@@ -4739,9 +4737,9 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:HO33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.6640625" customWidth="1"/>
     <col min="20" max="20" width="20.1640625" customWidth="1"/>
@@ -4753,206 +4751,206 @@
     <col min="188" max="188" width="17.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:223" x14ac:dyDescent="0.2">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:223" x14ac:dyDescent="0.35">
+      <c r="A1" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="F1" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="G1" s="25" t="s">
+      <c r="G1" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="H1" s="25" t="s">
+      <c r="H1" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="I1" s="25" t="s">
+      <c r="I1" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="J1" s="25" t="s">
+      <c r="J1" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="K1" s="25" t="s">
+      <c r="K1" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="L1" s="25" t="s">
+      <c r="L1" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="M1" s="25" t="s">
+      <c r="M1" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="N1" s="25" t="s">
+      <c r="N1" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="O1" s="25" t="s">
+      <c r="O1" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="P1" s="25" t="s">
+      <c r="P1" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="Q1" s="25" t="s">
+      <c r="Q1" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="R1" s="25" t="s">
+      <c r="R1" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="S1" s="25" t="s">
+      <c r="S1" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="T1" s="25" t="s">
+      <c r="T1" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="U1" s="25" t="s">
+      <c r="U1" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="V1" s="25" t="s">
+      <c r="V1" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="W1" s="25" t="s">
+      <c r="W1" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="X1" s="25" t="s">
+      <c r="X1" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="Y1" s="25" t="s">
+      <c r="Y1" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="Z1" s="25" t="s">
+      <c r="Z1" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="AA1" s="25" t="s">
+      <c r="AA1" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="AB1" s="25" t="s">
+      <c r="AB1" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="AC1" s="25" t="s">
+      <c r="AC1" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="AD1" s="25" t="s">
+      <c r="AD1" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="AE1" s="25" t="s">
+      <c r="AE1" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="AF1" s="25" t="s">
+      <c r="AF1" s="21" t="s">
         <v>142</v>
       </c>
-      <c r="AG1" s="25" t="s">
+      <c r="AG1" s="21" t="s">
         <v>143</v>
       </c>
-      <c r="AH1" s="25" t="s">
+      <c r="AH1" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="AI1" s="25" t="s">
+      <c r="AI1" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="AJ1" s="25" t="s">
+      <c r="AJ1" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="AK1" s="25" t="s">
+      <c r="AK1" s="21" t="s">
         <v>147</v>
       </c>
-      <c r="AL1" s="25" t="s">
+      <c r="AL1" s="21" t="s">
         <v>148</v>
       </c>
-      <c r="AM1" s="25" t="s">
+      <c r="AM1" s="21" t="s">
         <v>149</v>
       </c>
-      <c r="AN1" s="25" t="s">
+      <c r="AN1" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="AO1" s="25" t="s">
+      <c r="AO1" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="AP1" s="25" t="s">
+      <c r="AP1" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="AQ1" s="25" t="s">
+      <c r="AQ1" s="21" t="s">
         <v>153</v>
       </c>
-      <c r="AR1" s="25" t="s">
+      <c r="AR1" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="AS1" s="25" t="s">
+      <c r="AS1" s="21" t="s">
         <v>155</v>
       </c>
-      <c r="AT1" s="25" t="s">
+      <c r="AT1" s="21" t="s">
         <v>156</v>
       </c>
-      <c r="AU1" s="25" t="s">
+      <c r="AU1" s="21" t="s">
         <v>157</v>
       </c>
-      <c r="AV1" s="25" t="s">
+      <c r="AV1" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="AW1" s="25" t="s">
+      <c r="AW1" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="AX1" s="25" t="s">
+      <c r="AX1" s="21" t="s">
         <v>160</v>
       </c>
-      <c r="AY1" s="25" t="s">
+      <c r="AY1" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="AZ1" s="25" t="s">
+      <c r="AZ1" s="21" t="s">
         <v>162</v>
       </c>
-      <c r="BA1" s="25" t="s">
+      <c r="BA1" s="21" t="s">
         <v>163</v>
       </c>
-      <c r="BB1" s="25" t="s">
+      <c r="BB1" s="21" t="s">
         <v>164</v>
       </c>
-      <c r="BC1" s="25" t="s">
+      <c r="BC1" s="21" t="s">
         <v>165</v>
       </c>
-      <c r="BD1" s="25" t="s">
+      <c r="BD1" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="BE1" s="25" t="s">
+      <c r="BE1" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="BF1" s="25" t="s">
+      <c r="BF1" s="21" t="s">
         <v>168</v>
       </c>
-      <c r="BG1" s="25" t="s">
+      <c r="BG1" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="BH1" s="25" t="s">
+      <c r="BH1" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="BI1" s="25" t="s">
+      <c r="BI1" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="BJ1" s="25" t="s">
+      <c r="BJ1" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="BK1" s="25" t="s">
+      <c r="BK1" s="21" t="s">
         <v>173</v>
       </c>
-      <c r="BL1" s="25" t="s">
+      <c r="BL1" s="21" t="s">
         <v>174</v>
       </c>
-      <c r="BM1" s="25" t="s">
+      <c r="BM1" s="21" t="s">
         <v>175</v>
       </c>
-      <c r="BN1" s="25" t="s">
+      <c r="BN1" s="21" t="s">
         <v>176</v>
       </c>
-      <c r="BO1" s="25" t="s">
+      <c r="BO1" s="21" t="s">
         <v>177</v>
       </c>
       <c r="BQ1" t="s">
@@ -5421,206 +5419,206 @@
         <v>351</v>
       </c>
     </row>
-    <row r="2" spans="1:223" x14ac:dyDescent="0.2">
-      <c r="A2" s="25" t="s">
+    <row r="2" spans="1:223" x14ac:dyDescent="0.35">
+      <c r="A2" s="21" t="s">
         <v>178</v>
       </c>
-      <c r="B2" s="26">
+      <c r="B2" s="22">
         <v>42259</v>
       </c>
-      <c r="C2" s="25">
+      <c r="C2" s="21">
         <v>170</v>
       </c>
-      <c r="D2" s="26">
+      <c r="D2" s="22">
         <v>1273</v>
       </c>
-      <c r="E2" s="26">
+      <c r="E2" s="22">
         <v>5514953</v>
       </c>
-      <c r="F2" s="26">
+      <c r="F2" s="22">
         <v>5501</v>
       </c>
-      <c r="G2" s="25">
+      <c r="G2" s="21">
         <v>197</v>
       </c>
-      <c r="H2" s="26">
+      <c r="H2" s="22">
         <v>1598233</v>
       </c>
-      <c r="I2" s="26">
+      <c r="I2" s="22">
         <v>5820505</v>
       </c>
-      <c r="J2" s="25">
+      <c r="J2" s="21">
         <v>320</v>
       </c>
-      <c r="K2" s="26">
+      <c r="K2" s="22">
         <v>3297721</v>
       </c>
-      <c r="L2" s="26">
+      <c r="L2" s="22">
         <v>57746</v>
       </c>
-      <c r="M2" s="26">
+      <c r="M2" s="22">
         <v>94872</v>
       </c>
-      <c r="N2" s="26">
+      <c r="N2" s="22">
         <v>1776358</v>
       </c>
-      <c r="O2" s="26">
+      <c r="O2" s="22">
         <v>72206</v>
       </c>
-      <c r="P2" s="26">
+      <c r="P2" s="22">
         <v>8323</v>
       </c>
-      <c r="Q2" s="26">
+      <c r="Q2" s="22">
         <v>271779</v>
       </c>
-      <c r="R2" s="26">
+      <c r="R2" s="22">
         <v>13681</v>
       </c>
-      <c r="S2" s="26">
+      <c r="S2" s="22">
         <v>6012</v>
       </c>
-      <c r="T2" s="26">
+      <c r="T2" s="22">
         <v>126372</v>
       </c>
-      <c r="U2" s="25">
+      <c r="U2" s="21">
         <v>385</v>
       </c>
-      <c r="V2" s="26">
+      <c r="V2" s="22">
         <v>22037</v>
       </c>
-      <c r="W2" s="26">
+      <c r="W2" s="22">
         <v>66774</v>
       </c>
-      <c r="X2" s="26">
+      <c r="X2" s="22">
         <v>606057</v>
       </c>
-      <c r="Y2" s="26">
+      <c r="Y2" s="22">
         <v>49589</v>
       </c>
-      <c r="Z2" s="26">
+      <c r="Z2" s="22">
         <v>13719</v>
       </c>
-      <c r="AA2" s="26">
+      <c r="AA2" s="22">
         <v>2488</v>
       </c>
-      <c r="AB2" s="26">
+      <c r="AB2" s="22">
         <v>17048018</v>
       </c>
-      <c r="AC2" s="26">
+      <c r="AC2" s="22">
         <v>2605477</v>
       </c>
-      <c r="AD2" s="25">
+      <c r="AD2" s="21">
         <v>230</v>
       </c>
-      <c r="AE2" s="26">
+      <c r="AE2" s="22">
         <v>5818575</v>
       </c>
-      <c r="AF2" s="26">
+      <c r="AF2" s="22">
         <v>14256</v>
       </c>
-      <c r="AG2" s="26">
+      <c r="AG2" s="22">
         <v>2809</v>
       </c>
-      <c r="AH2" s="26">
+      <c r="AH2" s="22">
         <v>2316958</v>
       </c>
-      <c r="AI2" s="26">
+      <c r="AI2" s="22">
         <v>24458935</v>
       </c>
-      <c r="AJ2" s="26">
+      <c r="AJ2" s="22">
         <v>5187506</v>
       </c>
-      <c r="AK2" s="26">
+      <c r="AK2" s="22">
         <v>1651</v>
       </c>
-      <c r="AL2" s="26">
+      <c r="AL2" s="22">
         <v>5063</v>
       </c>
-      <c r="AM2" s="26">
+      <c r="AM2" s="22">
         <v>5342888</v>
       </c>
-      <c r="AN2" s="26">
+      <c r="AN2" s="22">
         <v>2130664</v>
       </c>
-      <c r="AO2" s="26">
+      <c r="AO2" s="22">
         <v>48515</v>
       </c>
-      <c r="AP2" s="26">
+      <c r="AP2" s="22">
         <v>386605</v>
       </c>
-      <c r="AQ2" s="26">
+      <c r="AQ2" s="22">
         <v>2257</v>
       </c>
-      <c r="AR2" s="26">
+      <c r="AR2" s="22">
         <v>17976</v>
       </c>
-      <c r="AS2" s="25" t="s">
+      <c r="AS2" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="AT2" s="25">
+      <c r="AT2" s="21">
         <v>833</v>
       </c>
-      <c r="AU2" s="26">
+      <c r="AU2" s="22">
         <v>1864</v>
       </c>
-      <c r="AV2" s="26">
+      <c r="AV2" s="22">
         <v>14860</v>
       </c>
-      <c r="AW2" s="26">
+      <c r="AW2" s="22">
         <v>12520</v>
       </c>
-      <c r="AX2" s="26">
+      <c r="AX2" s="22">
         <v>4067854</v>
       </c>
-      <c r="AY2" s="26">
+      <c r="AY2" s="22">
         <v>1176883</v>
       </c>
-      <c r="AZ2" s="26">
+      <c r="AZ2" s="22">
         <v>6649</v>
       </c>
-      <c r="BA2" s="26">
+      <c r="BA2" s="22">
         <v>49546</v>
       </c>
-      <c r="BB2" s="25">
+      <c r="BB2" s="21">
         <v>94</v>
       </c>
-      <c r="BC2" s="26">
+      <c r="BC2" s="22">
         <v>626739</v>
       </c>
-      <c r="BD2" s="26">
+      <c r="BD2" s="22">
         <v>123855</v>
       </c>
-      <c r="BE2" s="26">
+      <c r="BE2" s="22">
         <v>141439</v>
       </c>
-      <c r="BF2" s="26">
+      <c r="BF2" s="22">
         <v>1254</v>
       </c>
-      <c r="BG2" s="26">
+      <c r="BG2" s="22">
         <v>86218</v>
       </c>
-      <c r="BH2" s="26">
+      <c r="BH2" s="22">
         <v>9747204</v>
       </c>
-      <c r="BI2" s="26">
+      <c r="BI2" s="22">
         <v>2164602</v>
       </c>
-      <c r="BJ2" s="26">
+      <c r="BJ2" s="22">
         <v>1337</v>
       </c>
-      <c r="BK2" s="26">
+      <c r="BK2" s="22">
         <v>10231</v>
       </c>
-      <c r="BL2" s="26">
+      <c r="BL2" s="22">
         <v>670881</v>
       </c>
-      <c r="BM2" s="26">
+      <c r="BM2" s="22">
         <v>12713</v>
       </c>
-      <c r="BN2" s="26">
+      <c r="BN2" s="22">
         <v>1985264</v>
       </c>
-      <c r="BO2" s="26">
+      <c r="BO2" s="22">
         <v>3116962</v>
       </c>
       <c r="BQ2">
@@ -6089,206 +6087,206 @@
         <v>421555</v>
       </c>
     </row>
-    <row r="3" spans="1:223" x14ac:dyDescent="0.2">
-      <c r="A3" s="25" t="s">
+    <row r="3" spans="1:223" x14ac:dyDescent="0.35">
+      <c r="A3" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="B3" s="26">
+      <c r="B3" s="22">
         <v>47985</v>
       </c>
-      <c r="C3" s="25">
+      <c r="C3" s="21">
         <v>717</v>
       </c>
-      <c r="D3" s="26">
+      <c r="D3" s="22">
         <v>1293</v>
       </c>
-      <c r="E3" s="26">
+      <c r="E3" s="22">
         <v>6968369</v>
       </c>
-      <c r="F3" s="26">
+      <c r="F3" s="22">
         <v>6953</v>
       </c>
-      <c r="G3" s="25">
+      <c r="G3" s="21">
         <v>274</v>
       </c>
-      <c r="H3" s="26">
+      <c r="H3" s="22">
         <v>2115818</v>
       </c>
-      <c r="I3" s="26">
+      <c r="I3" s="22">
         <v>6910489</v>
       </c>
-      <c r="J3" s="25" t="s">
+      <c r="J3" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="K3" s="26">
+      <c r="K3" s="22">
         <v>3482424</v>
       </c>
-      <c r="L3" s="26">
+      <c r="L3" s="22">
         <v>73312</v>
       </c>
-      <c r="M3" s="26">
+      <c r="M3" s="22">
         <v>112907</v>
       </c>
-      <c r="N3" s="26">
+      <c r="N3" s="22">
         <v>1990264</v>
       </c>
-      <c r="O3" s="26">
+      <c r="O3" s="22">
         <v>73093</v>
       </c>
-      <c r="P3" s="26">
+      <c r="P3" s="22">
         <v>7603</v>
       </c>
-      <c r="Q3" s="26">
+      <c r="Q3" s="22">
         <v>301064</v>
       </c>
-      <c r="R3" s="26">
+      <c r="R3" s="22">
         <v>17501</v>
       </c>
-      <c r="S3" s="26">
+      <c r="S3" s="22">
         <v>2951</v>
       </c>
-      <c r="T3" s="26">
+      <c r="T3" s="22">
         <v>147270</v>
       </c>
-      <c r="U3" s="25">
+      <c r="U3" s="21">
         <v>575</v>
       </c>
-      <c r="V3" s="26">
+      <c r="V3" s="22">
         <v>27973</v>
       </c>
-      <c r="W3" s="26">
+      <c r="W3" s="22">
         <v>67239</v>
       </c>
-      <c r="X3" s="26">
+      <c r="X3" s="22">
         <v>647582</v>
       </c>
-      <c r="Y3" s="26">
+      <c r="Y3" s="22">
         <v>59782</v>
       </c>
-      <c r="Z3" s="26">
+      <c r="Z3" s="22">
         <v>13958</v>
       </c>
-      <c r="AA3" s="26">
+      <c r="AA3" s="22">
         <v>1895</v>
       </c>
-      <c r="AB3" s="26">
+      <c r="AB3" s="22">
         <v>20555738</v>
       </c>
-      <c r="AC3" s="26">
+      <c r="AC3" s="22">
         <v>3145047</v>
       </c>
-      <c r="AD3" s="26">
+      <c r="AD3" s="22">
         <v>1378</v>
       </c>
-      <c r="AE3" s="26">
+      <c r="AE3" s="22">
         <v>6918894</v>
       </c>
-      <c r="AF3" s="26">
+      <c r="AF3" s="22">
         <v>16535</v>
       </c>
-      <c r="AG3" s="26">
+      <c r="AG3" s="22">
         <v>5010</v>
       </c>
-      <c r="AH3" s="26">
+      <c r="AH3" s="22">
         <v>2936898</v>
       </c>
-      <c r="AI3" s="26">
+      <c r="AI3" s="22">
         <v>26075015</v>
       </c>
-      <c r="AJ3" s="26">
+      <c r="AJ3" s="22">
         <v>6540851</v>
       </c>
-      <c r="AK3" s="26">
+      <c r="AK3" s="22">
         <v>1348</v>
       </c>
-      <c r="AL3" s="26">
+      <c r="AL3" s="22">
         <v>7445</v>
       </c>
-      <c r="AM3" s="26">
+      <c r="AM3" s="22">
         <v>7034528</v>
       </c>
-      <c r="AN3" s="26">
+      <c r="AN3" s="22">
         <v>2441861</v>
       </c>
-      <c r="AO3" s="26">
+      <c r="AO3" s="22">
         <v>59103</v>
       </c>
-      <c r="AP3" s="26">
+      <c r="AP3" s="22">
         <v>576202</v>
       </c>
-      <c r="AQ3" s="26">
+      <c r="AQ3" s="22">
         <v>4123</v>
       </c>
-      <c r="AR3" s="26">
+      <c r="AR3" s="22">
         <v>25472</v>
       </c>
-      <c r="AS3" s="25" t="s">
+      <c r="AS3" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="AT3" s="25">
+      <c r="AT3" s="21">
         <v>554</v>
       </c>
-      <c r="AU3" s="26">
+      <c r="AU3" s="22">
         <v>1588</v>
       </c>
-      <c r="AV3" s="26">
+      <c r="AV3" s="22">
         <v>15052</v>
       </c>
-      <c r="AW3" s="26">
+      <c r="AW3" s="22">
         <v>11089</v>
       </c>
-      <c r="AX3" s="26">
+      <c r="AX3" s="22">
         <v>5071417</v>
       </c>
-      <c r="AY3" s="26">
+      <c r="AY3" s="22">
         <v>1538451</v>
       </c>
-      <c r="AZ3" s="26">
+      <c r="AZ3" s="22">
         <v>6770</v>
       </c>
-      <c r="BA3" s="26">
+      <c r="BA3" s="22">
         <v>70468</v>
       </c>
-      <c r="BB3" s="25">
+      <c r="BB3" s="21">
         <v>50</v>
       </c>
-      <c r="BC3" s="26">
+      <c r="BC3" s="22">
         <v>696459</v>
       </c>
-      <c r="BD3" s="26">
+      <c r="BD3" s="22">
         <v>128208</v>
       </c>
-      <c r="BE3" s="26">
+      <c r="BE3" s="22">
         <v>149787</v>
       </c>
-      <c r="BF3" s="26">
+      <c r="BF3" s="22">
         <v>1287</v>
       </c>
-      <c r="BG3" s="26">
+      <c r="BG3" s="22">
         <v>92821</v>
       </c>
-      <c r="BH3" s="26">
+      <c r="BH3" s="22">
         <v>11475799</v>
       </c>
-      <c r="BI3" s="26">
+      <c r="BI3" s="22">
         <v>2822004</v>
       </c>
-      <c r="BJ3" s="25">
+      <c r="BJ3" s="21">
         <v>293</v>
       </c>
-      <c r="BK3" s="26">
+      <c r="BK3" s="22">
         <v>11535</v>
       </c>
-      <c r="BL3" s="26">
+      <c r="BL3" s="22">
         <v>808383</v>
       </c>
-      <c r="BM3" s="26">
+      <c r="BM3" s="22">
         <v>14057</v>
       </c>
-      <c r="BN3" s="26">
+      <c r="BN3" s="22">
         <v>2391031</v>
       </c>
-      <c r="BO3" s="26">
+      <c r="BO3" s="22">
         <v>3893412</v>
       </c>
       <c r="BQ3">
@@ -6757,206 +6755,206 @@
         <v>513332</v>
       </c>
     </row>
-    <row r="4" spans="1:223" x14ac:dyDescent="0.2">
-      <c r="A4" s="25" t="s">
+    <row r="4" spans="1:223" x14ac:dyDescent="0.35">
+      <c r="A4" s="21" t="s">
         <v>181</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="22">
         <v>43320</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="22">
         <v>1724</v>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="21">
         <v>927</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="22">
         <v>5491218</v>
       </c>
-      <c r="F4" s="26">
+      <c r="F4" s="22">
         <v>6536</v>
       </c>
-      <c r="G4" s="25">
+      <c r="G4" s="21">
         <v>472</v>
       </c>
-      <c r="H4" s="26">
+      <c r="H4" s="22">
         <v>1818495</v>
       </c>
-      <c r="I4" s="26">
+      <c r="I4" s="22">
         <v>6228035</v>
       </c>
-      <c r="J4" s="25">
+      <c r="J4" s="21">
         <v>516</v>
       </c>
-      <c r="K4" s="26">
+      <c r="K4" s="22">
         <v>2669761</v>
       </c>
-      <c r="L4" s="26">
+      <c r="L4" s="22">
         <v>55353</v>
       </c>
-      <c r="M4" s="26">
+      <c r="M4" s="22">
         <v>101007</v>
       </c>
-      <c r="N4" s="26">
+      <c r="N4" s="22">
         <v>1849636</v>
       </c>
-      <c r="O4" s="26">
+      <c r="O4" s="22">
         <v>71130</v>
       </c>
-      <c r="P4" s="26">
+      <c r="P4" s="22">
         <v>6459</v>
       </c>
-      <c r="Q4" s="26">
+      <c r="Q4" s="22">
         <v>283738</v>
       </c>
-      <c r="R4" s="26">
+      <c r="R4" s="22">
         <v>16533</v>
       </c>
-      <c r="S4" s="26">
+      <c r="S4" s="22">
         <v>12724</v>
       </c>
-      <c r="T4" s="26">
+      <c r="T4" s="22">
         <v>128130</v>
       </c>
-      <c r="U4" s="25" t="s">
+      <c r="U4" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="V4" s="26">
+      <c r="V4" s="22">
         <v>21571</v>
       </c>
-      <c r="W4" s="26">
+      <c r="W4" s="22">
         <v>58365</v>
       </c>
-      <c r="X4" s="26">
+      <c r="X4" s="22">
         <v>548870</v>
       </c>
-      <c r="Y4" s="26">
+      <c r="Y4" s="22">
         <v>46502</v>
       </c>
-      <c r="Z4" s="26">
+      <c r="Z4" s="22">
         <v>14504</v>
       </c>
-      <c r="AA4" s="26">
+      <c r="AA4" s="22">
         <v>1646</v>
       </c>
-      <c r="AB4" s="26">
+      <c r="AB4" s="22">
         <v>18170408</v>
       </c>
-      <c r="AC4" s="26">
+      <c r="AC4" s="22">
         <v>2459685</v>
       </c>
-      <c r="AD4" s="25">
+      <c r="AD4" s="21">
         <v>825</v>
       </c>
-      <c r="AE4" s="26">
+      <c r="AE4" s="22">
         <v>6195471</v>
       </c>
-      <c r="AF4" s="26">
+      <c r="AF4" s="22">
         <v>13922</v>
       </c>
-      <c r="AG4" s="26">
+      <c r="AG4" s="22">
         <v>2576</v>
       </c>
-      <c r="AH4" s="26">
+      <c r="AH4" s="22">
         <v>2393601</v>
       </c>
-      <c r="AI4" s="26">
+      <c r="AI4" s="22">
         <v>25001239</v>
       </c>
-      <c r="AJ4" s="26">
+      <c r="AJ4" s="22">
         <v>4983924</v>
       </c>
-      <c r="AK4" s="26">
+      <c r="AK4" s="22">
         <v>1941</v>
       </c>
-      <c r="AL4" s="26">
+      <c r="AL4" s="22">
         <v>5774</v>
       </c>
-      <c r="AM4" s="26">
+      <c r="AM4" s="22">
         <v>5294218</v>
       </c>
-      <c r="AN4" s="26">
+      <c r="AN4" s="22">
         <v>1849991</v>
       </c>
-      <c r="AO4" s="26">
+      <c r="AO4" s="22">
         <v>43130</v>
       </c>
-      <c r="AP4" s="26">
+      <c r="AP4" s="22">
         <v>465683</v>
       </c>
-      <c r="AQ4" s="26">
+      <c r="AQ4" s="22">
         <v>2710</v>
       </c>
-      <c r="AR4" s="26">
+      <c r="AR4" s="22">
         <v>22325</v>
       </c>
-      <c r="AS4" s="25" t="s">
+      <c r="AS4" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="AT4" s="25">
+      <c r="AT4" s="21">
         <v>303</v>
       </c>
-      <c r="AU4" s="26">
+      <c r="AU4" s="22">
         <v>1594</v>
       </c>
-      <c r="AV4" s="26">
+      <c r="AV4" s="22">
         <v>11381</v>
       </c>
-      <c r="AW4" s="26">
+      <c r="AW4" s="22">
         <v>8623</v>
       </c>
-      <c r="AX4" s="26">
+      <c r="AX4" s="22">
         <v>4241180</v>
       </c>
-      <c r="AY4" s="26">
+      <c r="AY4" s="22">
         <v>1281409</v>
       </c>
-      <c r="AZ4" s="26">
+      <c r="AZ4" s="22">
         <v>7641</v>
       </c>
-      <c r="BA4" s="26">
+      <c r="BA4" s="22">
         <v>46238</v>
       </c>
-      <c r="BB4" s="25" t="s">
+      <c r="BB4" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="BC4" s="26">
+      <c r="BC4" s="22">
         <v>588522</v>
       </c>
-      <c r="BD4" s="26">
+      <c r="BD4" s="22">
         <v>103893</v>
       </c>
-      <c r="BE4" s="26">
+      <c r="BE4" s="22">
         <v>125853</v>
       </c>
-      <c r="BF4" s="25">
+      <c r="BF4" s="21">
         <v>535</v>
       </c>
-      <c r="BG4" s="26">
+      <c r="BG4" s="22">
         <v>85100</v>
       </c>
-      <c r="BH4" s="26">
+      <c r="BH4" s="22">
         <v>10254481</v>
       </c>
-      <c r="BI4" s="26">
+      <c r="BI4" s="22">
         <v>2282686</v>
       </c>
-      <c r="BJ4" s="25">
+      <c r="BJ4" s="21">
         <v>120</v>
       </c>
-      <c r="BK4" s="26">
+      <c r="BK4" s="22">
         <v>10650</v>
       </c>
-      <c r="BL4" s="26">
+      <c r="BL4" s="22">
         <v>710698</v>
       </c>
-      <c r="BM4" s="26">
+      <c r="BM4" s="22">
         <v>15493</v>
       </c>
-      <c r="BN4" s="26">
+      <c r="BN4" s="22">
         <v>2002362</v>
       </c>
-      <c r="BO4" s="26">
+      <c r="BO4" s="22">
         <v>3144953</v>
       </c>
       <c r="BQ4">
@@ -7425,206 +7423,206 @@
         <v>615388</v>
       </c>
     </row>
-    <row r="5" spans="1:223" x14ac:dyDescent="0.2">
-      <c r="A5" s="25" t="s">
+    <row r="5" spans="1:223" x14ac:dyDescent="0.35">
+      <c r="A5" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="B5" s="26">
+      <c r="B5" s="22">
         <v>56113</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="21">
         <v>534</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="21">
         <v>838</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="22">
         <v>8352748</v>
       </c>
-      <c r="F5" s="26">
+      <c r="F5" s="22">
         <v>6895</v>
       </c>
-      <c r="G5" s="25">
+      <c r="G5" s="21">
         <v>348</v>
       </c>
-      <c r="H5" s="26">
+      <c r="H5" s="22">
         <v>2282059</v>
       </c>
-      <c r="I5" s="26">
+      <c r="I5" s="22">
         <v>7370994</v>
       </c>
-      <c r="J5" s="25">
+      <c r="J5" s="21">
         <v>714</v>
       </c>
-      <c r="K5" s="26">
+      <c r="K5" s="22">
         <v>1466870</v>
       </c>
-      <c r="L5" s="26">
+      <c r="L5" s="22">
         <v>78215</v>
       </c>
-      <c r="M5" s="26">
+      <c r="M5" s="22">
         <v>117277</v>
       </c>
-      <c r="N5" s="26">
+      <c r="N5" s="22">
         <v>2241539</v>
       </c>
-      <c r="O5" s="26">
+      <c r="O5" s="22">
         <v>85019</v>
       </c>
-      <c r="P5" s="26">
+      <c r="P5" s="22">
         <v>7258</v>
       </c>
-      <c r="Q5" s="26">
+      <c r="Q5" s="22">
         <v>304791</v>
       </c>
-      <c r="R5" s="26">
+      <c r="R5" s="22">
         <v>17277</v>
       </c>
-      <c r="S5" s="26">
+      <c r="S5" s="22">
         <v>4502</v>
       </c>
-      <c r="T5" s="26">
+      <c r="T5" s="22">
         <v>158518</v>
       </c>
-      <c r="U5" s="25">
+      <c r="U5" s="21">
         <v>497</v>
       </c>
-      <c r="V5" s="26">
+      <c r="V5" s="22">
         <v>29437</v>
       </c>
-      <c r="W5" s="26">
+      <c r="W5" s="22">
         <v>82044</v>
       </c>
-      <c r="X5" s="26">
+      <c r="X5" s="22">
         <v>667927</v>
       </c>
-      <c r="Y5" s="26">
+      <c r="Y5" s="22">
         <v>58467</v>
       </c>
-      <c r="Z5" s="26">
+      <c r="Z5" s="22">
         <v>19411</v>
       </c>
-      <c r="AA5" s="26">
+      <c r="AA5" s="22">
         <v>3672</v>
       </c>
-      <c r="AB5" s="26">
+      <c r="AB5" s="22">
         <v>22104639</v>
       </c>
-      <c r="AC5" s="26">
+      <c r="AC5" s="22">
         <v>3937482</v>
       </c>
-      <c r="AD5" s="25">
+      <c r="AD5" s="21">
         <v>304</v>
       </c>
-      <c r="AE5" s="26">
+      <c r="AE5" s="22">
         <v>7425204</v>
       </c>
-      <c r="AF5" s="26">
+      <c r="AF5" s="22">
         <v>20598</v>
       </c>
-      <c r="AG5" s="26">
+      <c r="AG5" s="22">
         <v>2703</v>
       </c>
-      <c r="AH5" s="26">
+      <c r="AH5" s="22">
         <v>3284063</v>
       </c>
-      <c r="AI5" s="26">
+      <c r="AI5" s="22">
         <v>28771861</v>
       </c>
-      <c r="AJ5" s="26">
+      <c r="AJ5" s="22">
         <v>7726735</v>
       </c>
-      <c r="AK5" s="26">
+      <c r="AK5" s="22">
         <v>2810</v>
       </c>
-      <c r="AL5" s="26">
+      <c r="AL5" s="22">
         <v>7204</v>
       </c>
-      <c r="AM5" s="26">
+      <c r="AM5" s="22">
         <v>8037731</v>
       </c>
-      <c r="AN5" s="26">
+      <c r="AN5" s="22">
         <v>2689293</v>
       </c>
-      <c r="AO5" s="26">
+      <c r="AO5" s="22">
         <v>79415</v>
       </c>
-      <c r="AP5" s="26">
+      <c r="AP5" s="22">
         <v>707804</v>
       </c>
-      <c r="AQ5" s="26">
+      <c r="AQ5" s="22">
         <v>4146</v>
       </c>
-      <c r="AR5" s="26">
+      <c r="AR5" s="22">
         <v>29818</v>
       </c>
-      <c r="AS5" s="25">
+      <c r="AS5" s="21">
         <v>362</v>
       </c>
-      <c r="AT5" s="25">
+      <c r="AT5" s="21">
         <v>129</v>
       </c>
-      <c r="AU5" s="26">
+      <c r="AU5" s="22">
         <v>1917</v>
       </c>
-      <c r="AV5" s="26">
+      <c r="AV5" s="22">
         <v>14729</v>
       </c>
-      <c r="AW5" s="26">
+      <c r="AW5" s="22">
         <v>14513</v>
       </c>
-      <c r="AX5" s="26">
+      <c r="AX5" s="22">
         <v>5940547</v>
       </c>
-      <c r="AY5" s="26">
+      <c r="AY5" s="22">
         <v>1615906</v>
       </c>
-      <c r="AZ5" s="26">
+      <c r="AZ5" s="22">
         <v>8964</v>
       </c>
-      <c r="BA5" s="26">
+      <c r="BA5" s="22">
         <v>65657</v>
       </c>
-      <c r="BB5" s="25">
+      <c r="BB5" s="21">
         <v>281</v>
       </c>
-      <c r="BC5" s="26">
+      <c r="BC5" s="22">
         <v>765438</v>
       </c>
-      <c r="BD5" s="26">
+      <c r="BD5" s="22">
         <v>143203</v>
       </c>
-      <c r="BE5" s="26">
+      <c r="BE5" s="22">
         <v>155430</v>
       </c>
-      <c r="BF5" s="25">
+      <c r="BF5" s="21">
         <v>889</v>
       </c>
-      <c r="BG5" s="26">
+      <c r="BG5" s="22">
         <v>90305</v>
       </c>
-      <c r="BH5" s="26">
+      <c r="BH5" s="22">
         <v>11782346</v>
       </c>
-      <c r="BI5" s="26">
+      <c r="BI5" s="22">
         <v>3165134</v>
       </c>
-      <c r="BJ5" s="25">
+      <c r="BJ5" s="21">
         <v>707</v>
       </c>
-      <c r="BK5" s="26">
+      <c r="BK5" s="22">
         <v>9541</v>
       </c>
-      <c r="BL5" s="26">
+      <c r="BL5" s="22">
         <v>959423</v>
       </c>
-      <c r="BM5" s="26">
+      <c r="BM5" s="22">
         <v>18372</v>
       </c>
-      <c r="BN5" s="26">
+      <c r="BN5" s="22">
         <v>2770008</v>
       </c>
-      <c r="BO5" s="26">
+      <c r="BO5" s="22">
         <v>4575707</v>
       </c>
       <c r="BQ5">
@@ -8093,206 +8091,206 @@
         <v>544286</v>
       </c>
     </row>
-    <row r="6" spans="1:223" x14ac:dyDescent="0.2">
-      <c r="A6" s="25" t="s">
+    <row r="6" spans="1:223" x14ac:dyDescent="0.35">
+      <c r="A6" s="21" t="s">
         <v>183</v>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="22">
         <v>50905</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="21">
         <v>420</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="22">
         <v>2133</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="22">
         <v>6230600</v>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="22">
         <v>4091</v>
       </c>
-      <c r="G6" s="25">
+      <c r="G6" s="21">
         <v>395</v>
       </c>
-      <c r="H6" s="26">
+      <c r="H6" s="22">
         <v>1851598</v>
       </c>
-      <c r="I6" s="26">
+      <c r="I6" s="22">
         <v>5962472</v>
       </c>
-      <c r="J6" s="25" t="s">
+      <c r="J6" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="K6" s="26">
+      <c r="K6" s="22">
         <v>2991902</v>
       </c>
-      <c r="L6" s="26">
+      <c r="L6" s="22">
         <v>70013</v>
       </c>
-      <c r="M6" s="26">
+      <c r="M6" s="22">
         <v>98022</v>
       </c>
-      <c r="N6" s="26">
+      <c r="N6" s="22">
         <v>1863084</v>
       </c>
-      <c r="O6" s="26">
+      <c r="O6" s="22">
         <v>77345</v>
       </c>
-      <c r="P6" s="26">
+      <c r="P6" s="22">
         <v>6753</v>
       </c>
-      <c r="Q6" s="26">
+      <c r="Q6" s="22">
         <v>258571</v>
       </c>
-      <c r="R6" s="26">
+      <c r="R6" s="22">
         <v>17058</v>
       </c>
-      <c r="S6" s="26">
+      <c r="S6" s="22">
         <v>7043</v>
       </c>
-      <c r="T6" s="26">
+      <c r="T6" s="22">
         <v>130264</v>
       </c>
-      <c r="U6" s="25">
+      <c r="U6" s="21">
         <v>731</v>
       </c>
-      <c r="V6" s="26">
+      <c r="V6" s="22">
         <v>24405</v>
       </c>
-      <c r="W6" s="26">
+      <c r="W6" s="22">
         <v>75380</v>
       </c>
-      <c r="X6" s="26">
+      <c r="X6" s="22">
         <v>567932</v>
       </c>
-      <c r="Y6" s="26">
+      <c r="Y6" s="22">
         <v>50587</v>
       </c>
-      <c r="Z6" s="26">
+      <c r="Z6" s="22">
         <v>19833</v>
       </c>
-      <c r="AA6" s="26">
+      <c r="AA6" s="22">
         <v>2467</v>
       </c>
-      <c r="AB6" s="26">
+      <c r="AB6" s="22">
         <v>18358922</v>
       </c>
-      <c r="AC6" s="26">
+      <c r="AC6" s="22">
         <v>2987139</v>
       </c>
-      <c r="AD6" s="25">
+      <c r="AD6" s="21">
         <v>710</v>
       </c>
-      <c r="AE6" s="26">
+      <c r="AE6" s="22">
         <v>6064225</v>
       </c>
-      <c r="AF6" s="26">
+      <c r="AF6" s="22">
         <v>16907</v>
       </c>
-      <c r="AG6" s="26">
+      <c r="AG6" s="22">
         <v>3027</v>
       </c>
-      <c r="AH6" s="26">
+      <c r="AH6" s="22">
         <v>2622231</v>
       </c>
-      <c r="AI6" s="26">
+      <c r="AI6" s="22">
         <v>25560115</v>
       </c>
-      <c r="AJ6" s="26">
+      <c r="AJ6" s="22">
         <v>5763650</v>
       </c>
-      <c r="AK6" s="26">
+      <c r="AK6" s="22">
         <v>2158</v>
       </c>
-      <c r="AL6" s="26">
+      <c r="AL6" s="22">
         <v>8554</v>
       </c>
-      <c r="AM6" s="26">
+      <c r="AM6" s="22">
         <v>6213034</v>
       </c>
-      <c r="AN6" s="26">
+      <c r="AN6" s="22">
         <v>2047204</v>
       </c>
-      <c r="AO6" s="26">
+      <c r="AO6" s="22">
         <v>53233</v>
       </c>
-      <c r="AP6" s="26">
+      <c r="AP6" s="22">
         <v>650514</v>
       </c>
-      <c r="AQ6" s="26">
+      <c r="AQ6" s="22">
         <v>3106</v>
       </c>
-      <c r="AR6" s="26">
+      <c r="AR6" s="22">
         <v>25911</v>
       </c>
-      <c r="AS6" s="25" t="s">
+      <c r="AS6" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="AT6" s="26">
+      <c r="AT6" s="22">
         <v>1016</v>
       </c>
-      <c r="AU6" s="25">
+      <c r="AU6" s="21">
         <v>935</v>
       </c>
-      <c r="AV6" s="26">
+      <c r="AV6" s="22">
         <v>13032</v>
       </c>
-      <c r="AW6" s="26">
+      <c r="AW6" s="22">
         <v>14990</v>
       </c>
-      <c r="AX6" s="26">
+      <c r="AX6" s="22">
         <v>4976836</v>
       </c>
-      <c r="AY6" s="26">
+      <c r="AY6" s="22">
         <v>1295669</v>
       </c>
-      <c r="AZ6" s="26">
+      <c r="AZ6" s="22">
         <v>9616</v>
       </c>
-      <c r="BA6" s="26">
+      <c r="BA6" s="22">
         <v>57890</v>
       </c>
-      <c r="BB6" s="25" t="s">
+      <c r="BB6" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="BC6" s="26">
+      <c r="BC6" s="22">
         <v>611400</v>
       </c>
-      <c r="BD6" s="26">
+      <c r="BD6" s="22">
         <v>114639</v>
       </c>
-      <c r="BE6" s="26">
+      <c r="BE6" s="22">
         <v>129148</v>
       </c>
-      <c r="BF6" s="25">
+      <c r="BF6" s="21">
         <v>776</v>
       </c>
-      <c r="BG6" s="26">
+      <c r="BG6" s="22">
         <v>80347</v>
       </c>
-      <c r="BH6" s="26">
+      <c r="BH6" s="22">
         <v>9841636</v>
       </c>
-      <c r="BI6" s="26">
+      <c r="BI6" s="22">
         <v>2547959</v>
       </c>
-      <c r="BJ6" s="25">
+      <c r="BJ6" s="21">
         <v>171</v>
       </c>
-      <c r="BK6" s="26">
+      <c r="BK6" s="22">
         <v>9490</v>
       </c>
-      <c r="BL6" s="26">
+      <c r="BL6" s="22">
         <v>891849</v>
       </c>
-      <c r="BM6" s="26">
+      <c r="BM6" s="22">
         <v>16704</v>
       </c>
-      <c r="BN6" s="26">
+      <c r="BN6" s="22">
         <v>2377575</v>
       </c>
-      <c r="BO6" s="26">
+      <c r="BO6" s="22">
         <v>3515126</v>
       </c>
       <c r="BQ6">
@@ -8761,206 +8759,206 @@
         <v>573940</v>
       </c>
     </row>
-    <row r="7" spans="1:223" x14ac:dyDescent="0.2">
-      <c r="A7" s="25" t="s">
+    <row r="7" spans="1:223" x14ac:dyDescent="0.35">
+      <c r="A7" s="21" t="s">
         <v>184</v>
       </c>
-      <c r="B7" s="26">
+      <c r="B7" s="22">
         <v>35735</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="22">
         <v>2205</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="21">
         <v>612</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="22">
         <v>5653174</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="22">
         <v>4614</v>
       </c>
-      <c r="G7" s="25">
+      <c r="G7" s="21">
         <v>219</v>
       </c>
-      <c r="H7" s="26">
+      <c r="H7" s="22">
         <v>1560806</v>
       </c>
-      <c r="I7" s="26">
+      <c r="I7" s="22">
         <v>5523038</v>
       </c>
-      <c r="J7" s="25">
+      <c r="J7" s="21">
         <v>174</v>
       </c>
-      <c r="K7" s="26">
+      <c r="K7" s="22">
         <v>3002726</v>
       </c>
-      <c r="L7" s="26">
+      <c r="L7" s="22">
         <v>63325</v>
       </c>
-      <c r="M7" s="26">
+      <c r="M7" s="22">
         <v>91091</v>
       </c>
-      <c r="N7" s="26">
+      <c r="N7" s="22">
         <v>1703616</v>
       </c>
-      <c r="O7" s="26">
+      <c r="O7" s="22">
         <v>55356</v>
       </c>
-      <c r="P7" s="26">
+      <c r="P7" s="22">
         <v>6588</v>
       </c>
-      <c r="Q7" s="26">
+      <c r="Q7" s="22">
         <v>229745</v>
       </c>
-      <c r="R7" s="26">
+      <c r="R7" s="22">
         <v>13915</v>
       </c>
-      <c r="S7" s="26">
+      <c r="S7" s="22">
         <v>15256</v>
       </c>
-      <c r="T7" s="26">
+      <c r="T7" s="22">
         <v>114891</v>
       </c>
-      <c r="U7" s="25">
+      <c r="U7" s="21">
         <v>216</v>
       </c>
-      <c r="V7" s="26">
+      <c r="V7" s="22">
         <v>26539</v>
       </c>
-      <c r="W7" s="26">
+      <c r="W7" s="22">
         <v>59459</v>
       </c>
-      <c r="X7" s="26">
+      <c r="X7" s="22">
         <v>538032</v>
       </c>
-      <c r="Y7" s="26">
+      <c r="Y7" s="22">
         <v>39071</v>
       </c>
-      <c r="Z7" s="26">
+      <c r="Z7" s="22">
         <v>17977</v>
       </c>
-      <c r="AA7" s="26">
+      <c r="AA7" s="22">
         <v>3582</v>
       </c>
-      <c r="AB7" s="26">
+      <c r="AB7" s="22">
         <v>15677667</v>
       </c>
-      <c r="AC7" s="26">
+      <c r="AC7" s="22">
         <v>2811493</v>
       </c>
-      <c r="AD7" s="25">
+      <c r="AD7" s="21">
         <v>681</v>
       </c>
-      <c r="AE7" s="26">
+      <c r="AE7" s="22">
         <v>5365825</v>
       </c>
-      <c r="AF7" s="26">
+      <c r="AF7" s="22">
         <v>16277</v>
       </c>
-      <c r="AG7" s="25">
+      <c r="AG7" s="21">
         <v>961</v>
       </c>
-      <c r="AH7" s="26">
+      <c r="AH7" s="22">
         <v>2272609</v>
       </c>
-      <c r="AI7" s="26">
+      <c r="AI7" s="22">
         <v>21789922</v>
       </c>
-      <c r="AJ7" s="26">
+      <c r="AJ7" s="22">
         <v>5040180</v>
       </c>
-      <c r="AK7" s="26">
+      <c r="AK7" s="22">
         <v>2311</v>
       </c>
-      <c r="AL7" s="26">
+      <c r="AL7" s="22">
         <v>4456</v>
       </c>
-      <c r="AM7" s="26">
+      <c r="AM7" s="22">
         <v>5377106</v>
       </c>
-      <c r="AN7" s="26">
+      <c r="AN7" s="22">
         <v>2023093</v>
       </c>
-      <c r="AO7" s="26">
+      <c r="AO7" s="22">
         <v>46358</v>
       </c>
-      <c r="AP7" s="26">
+      <c r="AP7" s="22">
         <v>537140</v>
       </c>
-      <c r="AQ7" s="26">
+      <c r="AQ7" s="22">
         <v>3428</v>
       </c>
-      <c r="AR7" s="26">
+      <c r="AR7" s="22">
         <v>25026</v>
       </c>
-      <c r="AS7" s="25">
+      <c r="AS7" s="21">
         <v>336</v>
       </c>
-      <c r="AT7" s="25">
+      <c r="AT7" s="21">
         <v>482</v>
       </c>
-      <c r="AU7" s="26">
+      <c r="AU7" s="22">
         <v>1354</v>
       </c>
-      <c r="AV7" s="26">
+      <c r="AV7" s="22">
         <v>9337</v>
       </c>
-      <c r="AW7" s="26">
+      <c r="AW7" s="22">
         <v>10884</v>
       </c>
-      <c r="AX7" s="26">
+      <c r="AX7" s="22">
         <v>4579980</v>
       </c>
-      <c r="AY7" s="26">
+      <c r="AY7" s="22">
         <v>1062065</v>
       </c>
-      <c r="AZ7" s="26">
+      <c r="AZ7" s="22">
         <v>5395</v>
       </c>
-      <c r="BA7" s="26">
+      <c r="BA7" s="22">
         <v>36621</v>
       </c>
-      <c r="BB7" s="25" t="s">
+      <c r="BB7" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="BC7" s="26">
+      <c r="BC7" s="22">
         <v>562235</v>
       </c>
-      <c r="BD7" s="26">
+      <c r="BD7" s="22">
         <v>108434</v>
       </c>
-      <c r="BE7" s="26">
+      <c r="BE7" s="22">
         <v>126961</v>
       </c>
-      <c r="BF7" s="26">
+      <c r="BF7" s="22">
         <v>1007</v>
       </c>
-      <c r="BG7" s="26">
+      <c r="BG7" s="22">
         <v>86283</v>
       </c>
-      <c r="BH7" s="26">
+      <c r="BH7" s="22">
         <v>8963814</v>
       </c>
-      <c r="BI7" s="26">
+      <c r="BI7" s="22">
         <v>2198445</v>
       </c>
-      <c r="BJ7" s="25">
+      <c r="BJ7" s="21">
         <v>252</v>
       </c>
-      <c r="BK7" s="26">
+      <c r="BK7" s="22">
         <v>10006</v>
       </c>
-      <c r="BL7" s="26">
+      <c r="BL7" s="22">
         <v>844699</v>
       </c>
-      <c r="BM7" s="26">
+      <c r="BM7" s="22">
         <v>12726</v>
       </c>
-      <c r="BN7" s="26">
+      <c r="BN7" s="22">
         <v>2223925</v>
       </c>
-      <c r="BO7" s="26">
+      <c r="BO7" s="22">
         <v>3114532</v>
       </c>
       <c r="BQ7">
@@ -9429,206 +9427,206 @@
         <v>459016</v>
       </c>
     </row>
-    <row r="8" spans="1:223" x14ac:dyDescent="0.2">
-      <c r="A8" s="25" t="s">
+    <row r="8" spans="1:223" x14ac:dyDescent="0.35">
+      <c r="A8" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="B8" s="26">
+      <c r="B8" s="22">
         <v>46080</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="22">
         <v>1602</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="21">
         <v>989</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="22">
         <v>5798438</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="22">
         <v>3469</v>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="21">
         <v>423</v>
       </c>
-      <c r="H8" s="26">
+      <c r="H8" s="22">
         <v>1563635</v>
       </c>
-      <c r="I8" s="26">
+      <c r="I8" s="22">
         <v>5724225</v>
       </c>
-      <c r="J8" s="25">
+      <c r="J8" s="21">
         <v>240</v>
       </c>
-      <c r="K8" s="26">
+      <c r="K8" s="22">
         <v>2898473</v>
       </c>
-      <c r="L8" s="26">
+      <c r="L8" s="22">
         <v>78694</v>
       </c>
-      <c r="M8" s="26">
+      <c r="M8" s="22">
         <v>92393</v>
       </c>
-      <c r="N8" s="26">
+      <c r="N8" s="22">
         <v>1873830</v>
       </c>
-      <c r="O8" s="26">
+      <c r="O8" s="22">
         <v>58638</v>
       </c>
-      <c r="P8" s="26">
+      <c r="P8" s="22">
         <v>5828</v>
       </c>
-      <c r="Q8" s="26">
+      <c r="Q8" s="22">
         <v>266369</v>
       </c>
-      <c r="R8" s="26">
+      <c r="R8" s="22">
         <v>11257</v>
       </c>
-      <c r="S8" s="26">
+      <c r="S8" s="22">
         <v>5628</v>
       </c>
-      <c r="T8" s="26">
+      <c r="T8" s="22">
         <v>118953</v>
       </c>
-      <c r="U8" s="25">
+      <c r="U8" s="21">
         <v>210</v>
       </c>
-      <c r="V8" s="26">
+      <c r="V8" s="22">
         <v>21416</v>
       </c>
-      <c r="W8" s="26">
+      <c r="W8" s="22">
         <v>61272</v>
       </c>
-      <c r="X8" s="26">
+      <c r="X8" s="22">
         <v>581195</v>
       </c>
-      <c r="Y8" s="26">
+      <c r="Y8" s="22">
         <v>49024</v>
       </c>
-      <c r="Z8" s="26">
+      <c r="Z8" s="22">
         <v>17343</v>
       </c>
-      <c r="AA8" s="26">
+      <c r="AA8" s="22">
         <v>4053</v>
       </c>
-      <c r="AB8" s="26">
+      <c r="AB8" s="22">
         <v>15964064</v>
       </c>
-      <c r="AC8" s="26">
+      <c r="AC8" s="22">
         <v>3181000</v>
       </c>
-      <c r="AD8" s="26">
+      <c r="AD8" s="22">
         <v>1092</v>
       </c>
-      <c r="AE8" s="26">
+      <c r="AE8" s="22">
         <v>5810836</v>
       </c>
-      <c r="AF8" s="26">
+      <c r="AF8" s="22">
         <v>17945</v>
       </c>
-      <c r="AG8" s="26">
+      <c r="AG8" s="22">
         <v>1777</v>
       </c>
-      <c r="AH8" s="26">
+      <c r="AH8" s="22">
         <v>2444708</v>
       </c>
-      <c r="AI8" s="26">
+      <c r="AI8" s="22">
         <v>24206025</v>
       </c>
-      <c r="AJ8" s="26">
+      <c r="AJ8" s="22">
         <v>5264918</v>
       </c>
-      <c r="AK8" s="26">
+      <c r="AK8" s="22">
         <v>1469</v>
       </c>
-      <c r="AL8" s="26">
+      <c r="AL8" s="22">
         <v>6316</v>
       </c>
-      <c r="AM8" s="26">
+      <c r="AM8" s="22">
         <v>5552838</v>
       </c>
-      <c r="AN8" s="26">
+      <c r="AN8" s="22">
         <v>2266590</v>
       </c>
-      <c r="AO8" s="26">
+      <c r="AO8" s="22">
         <v>55192</v>
       </c>
-      <c r="AP8" s="26">
+      <c r="AP8" s="22">
         <v>456545</v>
       </c>
-      <c r="AQ8" s="26">
+      <c r="AQ8" s="22">
         <v>2377</v>
       </c>
-      <c r="AR8" s="26">
+      <c r="AR8" s="22">
         <v>24632</v>
       </c>
-      <c r="AS8" s="25">
+      <c r="AS8" s="21">
         <v>105</v>
       </c>
-      <c r="AT8" s="25">
+      <c r="AT8" s="21">
         <v>126</v>
       </c>
-      <c r="AU8" s="25">
+      <c r="AU8" s="21">
         <v>726</v>
       </c>
-      <c r="AV8" s="26">
+      <c r="AV8" s="22">
         <v>10126</v>
       </c>
-      <c r="AW8" s="26">
+      <c r="AW8" s="22">
         <v>14420</v>
       </c>
-      <c r="AX8" s="26">
+      <c r="AX8" s="22">
         <v>4337487</v>
       </c>
-      <c r="AY8" s="26">
+      <c r="AY8" s="22">
         <v>925952</v>
       </c>
-      <c r="AZ8" s="26">
+      <c r="AZ8" s="22">
         <v>9763</v>
       </c>
-      <c r="BA8" s="26">
+      <c r="BA8" s="22">
         <v>68357</v>
       </c>
-      <c r="BB8" s="25">
+      <c r="BB8" s="21">
         <v>109</v>
       </c>
-      <c r="BC8" s="26">
+      <c r="BC8" s="22">
         <v>697766</v>
       </c>
-      <c r="BD8" s="26">
+      <c r="BD8" s="22">
         <v>113784</v>
       </c>
-      <c r="BE8" s="26">
+      <c r="BE8" s="22">
         <v>128725</v>
       </c>
-      <c r="BF8" s="25">
+      <c r="BF8" s="21">
         <v>854</v>
       </c>
-      <c r="BG8" s="26">
+      <c r="BG8" s="22">
         <v>77727</v>
       </c>
-      <c r="BH8" s="26">
+      <c r="BH8" s="22">
         <v>8822894</v>
       </c>
-      <c r="BI8" s="26">
+      <c r="BI8" s="22">
         <v>2300808</v>
       </c>
-      <c r="BJ8" s="25">
+      <c r="BJ8" s="21">
         <v>573</v>
       </c>
-      <c r="BK8" s="26">
+      <c r="BK8" s="22">
         <v>10359</v>
       </c>
-      <c r="BL8" s="26">
+      <c r="BL8" s="22">
         <v>758502</v>
       </c>
-      <c r="BM8" s="26">
+      <c r="BM8" s="22">
         <v>7843</v>
       </c>
-      <c r="BN8" s="26">
+      <c r="BN8" s="22">
         <v>2059046</v>
       </c>
-      <c r="BO8" s="26">
+      <c r="BO8" s="22">
         <v>3219804</v>
       </c>
       <c r="BQ8">
@@ -10097,206 +10095,206 @@
         <v>392728</v>
       </c>
     </row>
-    <row r="9" spans="1:223" x14ac:dyDescent="0.2">
-      <c r="A9" s="25" t="s">
+    <row r="9" spans="1:223" x14ac:dyDescent="0.35">
+      <c r="A9" s="21" t="s">
         <v>186</v>
       </c>
-      <c r="B9" s="26">
+      <c r="B9" s="22">
         <v>46605</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="22">
         <v>1543</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="22">
         <v>1642</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="22">
         <v>5319844</v>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="22">
         <v>4204</v>
       </c>
-      <c r="G9" s="25">
+      <c r="G9" s="21">
         <v>243</v>
       </c>
-      <c r="H9" s="26">
+      <c r="H9" s="22">
         <v>1542377</v>
       </c>
-      <c r="I9" s="26">
+      <c r="I9" s="22">
         <v>5961429</v>
       </c>
-      <c r="J9" s="25">
+      <c r="J9" s="21">
         <v>440</v>
       </c>
-      <c r="K9" s="26">
+      <c r="K9" s="22">
         <v>3113059</v>
       </c>
-      <c r="L9" s="26">
+      <c r="L9" s="22">
         <v>65467</v>
       </c>
-      <c r="M9" s="26">
+      <c r="M9" s="22">
         <v>90048</v>
       </c>
-      <c r="N9" s="26">
+      <c r="N9" s="22">
         <v>1780194</v>
       </c>
-      <c r="O9" s="26">
+      <c r="O9" s="22">
         <v>58747</v>
       </c>
-      <c r="P9" s="26">
+      <c r="P9" s="22">
         <v>5925</v>
       </c>
-      <c r="Q9" s="26">
+      <c r="Q9" s="22">
         <v>263349</v>
       </c>
-      <c r="R9" s="26">
+      <c r="R9" s="22">
         <v>14276</v>
       </c>
-      <c r="S9" s="26">
+      <c r="S9" s="22">
         <v>1277</v>
       </c>
-      <c r="T9" s="26">
+      <c r="T9" s="22">
         <v>110075</v>
       </c>
-      <c r="U9" s="25">
+      <c r="U9" s="21">
         <v>401</v>
       </c>
-      <c r="V9" s="26">
+      <c r="V9" s="22">
         <v>25302</v>
       </c>
-      <c r="W9" s="26">
+      <c r="W9" s="22">
         <v>51172</v>
       </c>
-      <c r="X9" s="26">
+      <c r="X9" s="22">
         <v>578368</v>
       </c>
-      <c r="Y9" s="26">
+      <c r="Y9" s="22">
         <v>53209</v>
       </c>
-      <c r="Z9" s="26">
+      <c r="Z9" s="22">
         <v>13234</v>
       </c>
-      <c r="AA9" s="26">
+      <c r="AA9" s="22">
         <v>2032</v>
       </c>
-      <c r="AB9" s="26">
+      <c r="AB9" s="22">
         <v>14985489</v>
       </c>
-      <c r="AC9" s="26">
+      <c r="AC9" s="22">
         <v>2795217</v>
       </c>
-      <c r="AD9" s="25">
+      <c r="AD9" s="21">
         <v>228</v>
       </c>
-      <c r="AE9" s="26">
+      <c r="AE9" s="22">
         <v>5954198</v>
       </c>
-      <c r="AF9" s="26">
+      <c r="AF9" s="22">
         <v>16001</v>
       </c>
-      <c r="AG9" s="26">
+      <c r="AG9" s="22">
         <v>2101</v>
       </c>
-      <c r="AH9" s="26">
+      <c r="AH9" s="22">
         <v>2222343</v>
       </c>
-      <c r="AI9" s="26">
+      <c r="AI9" s="22">
         <v>21651987</v>
       </c>
-      <c r="AJ9" s="26">
+      <c r="AJ9" s="22">
         <v>4843937</v>
       </c>
-      <c r="AK9" s="26">
+      <c r="AK9" s="22">
         <v>2027</v>
       </c>
-      <c r="AL9" s="26">
+      <c r="AL9" s="22">
         <v>5070</v>
       </c>
-      <c r="AM9" s="26">
+      <c r="AM9" s="22">
         <v>5159388</v>
       </c>
-      <c r="AN9" s="26">
+      <c r="AN9" s="22">
         <v>2059425</v>
       </c>
-      <c r="AO9" s="26">
+      <c r="AO9" s="22">
         <v>46494</v>
       </c>
-      <c r="AP9" s="26">
+      <c r="AP9" s="22">
         <v>443689</v>
       </c>
-      <c r="AQ9" s="26">
+      <c r="AQ9" s="22">
         <v>2863</v>
       </c>
-      <c r="AR9" s="26">
+      <c r="AR9" s="22">
         <v>23173</v>
       </c>
-      <c r="AS9" s="25" t="s">
+      <c r="AS9" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="AT9" s="25">
+      <c r="AT9" s="21">
         <v>304</v>
       </c>
-      <c r="AU9" s="25">
+      <c r="AU9" s="21">
         <v>977</v>
       </c>
-      <c r="AV9" s="26">
+      <c r="AV9" s="22">
         <v>10516</v>
       </c>
-      <c r="AW9" s="26">
+      <c r="AW9" s="22">
         <v>15473</v>
       </c>
-      <c r="AX9" s="26">
+      <c r="AX9" s="22">
         <v>4301706</v>
       </c>
-      <c r="AY9" s="26">
+      <c r="AY9" s="22">
         <v>995830</v>
       </c>
-      <c r="AZ9" s="26">
+      <c r="AZ9" s="22">
         <v>9587</v>
       </c>
-      <c r="BA9" s="26">
+      <c r="BA9" s="22">
         <v>62570</v>
       </c>
-      <c r="BB9" s="25" t="s">
+      <c r="BB9" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="BC9" s="26">
+      <c r="BC9" s="22">
         <v>619663</v>
       </c>
-      <c r="BD9" s="26">
+      <c r="BD9" s="22">
         <v>116839</v>
       </c>
-      <c r="BE9" s="26">
+      <c r="BE9" s="22">
         <v>132232</v>
       </c>
-      <c r="BF9" s="25">
+      <c r="BF9" s="21">
         <v>370</v>
       </c>
-      <c r="BG9" s="26">
+      <c r="BG9" s="22">
         <v>79695</v>
       </c>
-      <c r="BH9" s="26">
+      <c r="BH9" s="22">
         <v>9208109</v>
       </c>
-      <c r="BI9" s="26">
+      <c r="BI9" s="22">
         <v>2143048</v>
       </c>
-      <c r="BJ9" s="25">
+      <c r="BJ9" s="21">
         <v>643</v>
       </c>
-      <c r="BK9" s="26">
+      <c r="BK9" s="22">
         <v>11588</v>
       </c>
-      <c r="BL9" s="26">
+      <c r="BL9" s="22">
         <v>762084</v>
       </c>
-      <c r="BM9" s="26">
+      <c r="BM9" s="22">
         <v>10775</v>
       </c>
-      <c r="BN9" s="26">
+      <c r="BN9" s="22">
         <v>2085998</v>
       </c>
-      <c r="BO9" s="26">
+      <c r="BO9" s="22">
         <v>2986194</v>
       </c>
       <c r="BQ9">
@@ -10765,206 +10763,206 @@
         <v>492738</v>
       </c>
     </row>
-    <row r="10" spans="1:223" x14ac:dyDescent="0.2">
-      <c r="A10" s="25" t="s">
+    <row r="10" spans="1:223" x14ac:dyDescent="0.35">
+      <c r="A10" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="22">
         <v>46144</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="21">
         <v>214</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="22">
         <v>1370</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="22">
         <v>4771958</v>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="22">
         <v>1702</v>
       </c>
-      <c r="G10" s="25">
+      <c r="G10" s="21">
         <v>406</v>
       </c>
-      <c r="H10" s="26">
+      <c r="H10" s="22">
         <v>1449119</v>
       </c>
-      <c r="I10" s="26">
+      <c r="I10" s="22">
         <v>5011269</v>
       </c>
-      <c r="J10" s="25" t="s">
+      <c r="J10" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="K10" s="26">
+      <c r="K10" s="22">
         <v>3225425</v>
       </c>
-      <c r="L10" s="26">
+      <c r="L10" s="22">
         <v>62332</v>
       </c>
-      <c r="M10" s="26">
+      <c r="M10" s="22">
         <v>77009</v>
       </c>
-      <c r="N10" s="26">
+      <c r="N10" s="22">
         <v>1642746</v>
       </c>
-      <c r="O10" s="26">
+      <c r="O10" s="22">
         <v>55163</v>
       </c>
-      <c r="P10" s="26">
+      <c r="P10" s="22">
         <v>5619</v>
       </c>
-      <c r="Q10" s="26">
+      <c r="Q10" s="22">
         <v>227763</v>
       </c>
-      <c r="R10" s="26">
+      <c r="R10" s="22">
         <v>11121</v>
       </c>
-      <c r="S10" s="26">
+      <c r="S10" s="22">
         <v>9930</v>
       </c>
-      <c r="T10" s="26">
+      <c r="T10" s="22">
         <v>99119</v>
       </c>
-      <c r="U10" s="25">
+      <c r="U10" s="21">
         <v>210</v>
       </c>
-      <c r="V10" s="26">
+      <c r="V10" s="22">
         <v>27365</v>
       </c>
-      <c r="W10" s="26">
+      <c r="W10" s="22">
         <v>61805</v>
       </c>
-      <c r="X10" s="26">
+      <c r="X10" s="22">
         <v>592120</v>
       </c>
-      <c r="Y10" s="26">
+      <c r="Y10" s="22">
         <v>49020</v>
       </c>
-      <c r="Z10" s="26">
+      <c r="Z10" s="22">
         <v>15289</v>
       </c>
-      <c r="AA10" s="26">
+      <c r="AA10" s="22">
         <v>3032</v>
       </c>
-      <c r="AB10" s="26">
+      <c r="AB10" s="22">
         <v>13847970</v>
       </c>
-      <c r="AC10" s="26">
+      <c r="AC10" s="22">
         <v>2587547</v>
       </c>
-      <c r="AD10" s="25">
+      <c r="AD10" s="21">
         <v>508</v>
       </c>
-      <c r="AE10" s="26">
+      <c r="AE10" s="22">
         <v>5090152</v>
       </c>
-      <c r="AF10" s="26">
+      <c r="AF10" s="22">
         <v>14609</v>
       </c>
-      <c r="AG10" s="26">
+      <c r="AG10" s="22">
         <v>1096</v>
       </c>
-      <c r="AH10" s="26">
+      <c r="AH10" s="22">
         <v>2025074</v>
       </c>
-      <c r="AI10" s="26">
+      <c r="AI10" s="22">
         <v>21206351</v>
       </c>
-      <c r="AJ10" s="26">
+      <c r="AJ10" s="22">
         <v>4378608</v>
       </c>
-      <c r="AK10" s="26">
+      <c r="AK10" s="22">
         <v>1101</v>
       </c>
-      <c r="AL10" s="26">
+      <c r="AL10" s="22">
         <v>4280</v>
       </c>
-      <c r="AM10" s="26">
+      <c r="AM10" s="22">
         <v>4586340</v>
       </c>
-      <c r="AN10" s="26">
+      <c r="AN10" s="22">
         <v>2038966</v>
       </c>
-      <c r="AO10" s="26">
+      <c r="AO10" s="22">
         <v>42955</v>
       </c>
-      <c r="AP10" s="26">
+      <c r="AP10" s="22">
         <v>422605</v>
       </c>
-      <c r="AQ10" s="26">
+      <c r="AQ10" s="22">
         <v>3984</v>
       </c>
-      <c r="AR10" s="26">
+      <c r="AR10" s="22">
         <v>18945</v>
       </c>
-      <c r="AS10" s="25">
+      <c r="AS10" s="21">
         <v>182</v>
       </c>
-      <c r="AT10" s="25">
+      <c r="AT10" s="21">
         <v>258</v>
       </c>
-      <c r="AU10" s="26">
+      <c r="AU10" s="22">
         <v>1494</v>
       </c>
-      <c r="AV10" s="26">
+      <c r="AV10" s="22">
         <v>10614</v>
       </c>
-      <c r="AW10" s="26">
+      <c r="AW10" s="22">
         <v>11818</v>
       </c>
-      <c r="AX10" s="26">
+      <c r="AX10" s="22">
         <v>3733725</v>
       </c>
-      <c r="AY10" s="26">
+      <c r="AY10" s="22">
         <v>876560</v>
       </c>
-      <c r="AZ10" s="26">
+      <c r="AZ10" s="22">
         <v>9884</v>
       </c>
-      <c r="BA10" s="26">
+      <c r="BA10" s="22">
         <v>65955</v>
       </c>
-      <c r="BB10" s="25" t="s">
+      <c r="BB10" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="BC10" s="26">
+      <c r="BC10" s="22">
         <v>550339</v>
       </c>
-      <c r="BD10" s="26">
+      <c r="BD10" s="22">
         <v>117994</v>
       </c>
-      <c r="BE10" s="26">
+      <c r="BE10" s="22">
         <v>132280</v>
       </c>
-      <c r="BF10" s="25">
+      <c r="BF10" s="21">
         <v>825</v>
       </c>
-      <c r="BG10" s="26">
+      <c r="BG10" s="22">
         <v>84111</v>
       </c>
-      <c r="BH10" s="26">
+      <c r="BH10" s="22">
         <v>7500567</v>
       </c>
-      <c r="BI10" s="26">
+      <c r="BI10" s="22">
         <v>1930097</v>
       </c>
-      <c r="BJ10" s="25">
+      <c r="BJ10" s="21">
         <v>209</v>
       </c>
-      <c r="BK10" s="26">
+      <c r="BK10" s="22">
         <v>10553</v>
       </c>
-      <c r="BL10" s="26">
+      <c r="BL10" s="22">
         <v>678220</v>
       </c>
-      <c r="BM10" s="26">
+      <c r="BM10" s="22">
         <v>10831</v>
       </c>
-      <c r="BN10" s="26">
+      <c r="BN10" s="22">
         <v>1834704</v>
       </c>
-      <c r="BO10" s="26">
+      <c r="BO10" s="22">
         <v>2691873</v>
       </c>
       <c r="BQ10">
@@ -11433,206 +11431,206 @@
         <v>393574</v>
       </c>
     </row>
-    <row r="11" spans="1:223" x14ac:dyDescent="0.2">
-      <c r="A11" s="25" t="s">
+    <row r="11" spans="1:223" x14ac:dyDescent="0.35">
+      <c r="A11" s="21" t="s">
         <v>188</v>
       </c>
-      <c r="B11" s="26">
+      <c r="B11" s="22">
         <v>39574</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="21">
         <v>780</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="22">
         <v>1589</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="22">
         <v>4151346</v>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="22">
         <v>1535</v>
       </c>
-      <c r="G11" s="25">
+      <c r="G11" s="21">
         <v>220</v>
       </c>
-      <c r="H11" s="26">
+      <c r="H11" s="22">
         <v>1073082</v>
       </c>
-      <c r="I11" s="26">
+      <c r="I11" s="22">
         <v>4087562</v>
       </c>
-      <c r="J11" s="25">
+      <c r="J11" s="21">
         <v>355</v>
       </c>
-      <c r="K11" s="26">
+      <c r="K11" s="22">
         <v>2945234</v>
       </c>
-      <c r="L11" s="26">
+      <c r="L11" s="22">
         <v>53413</v>
       </c>
-      <c r="M11" s="26">
+      <c r="M11" s="22">
         <v>68998</v>
       </c>
-      <c r="N11" s="26">
+      <c r="N11" s="22">
         <v>1370497</v>
       </c>
-      <c r="O11" s="26">
+      <c r="O11" s="22">
         <v>61075</v>
       </c>
-      <c r="P11" s="26">
+      <c r="P11" s="22">
         <v>4626</v>
       </c>
-      <c r="Q11" s="26">
+      <c r="Q11" s="22">
         <v>197959</v>
       </c>
-      <c r="R11" s="26">
+      <c r="R11" s="22">
         <v>10242</v>
       </c>
-      <c r="S11" s="26">
+      <c r="S11" s="22">
         <v>7909</v>
       </c>
-      <c r="T11" s="26">
+      <c r="T11" s="22">
         <v>86420</v>
       </c>
-      <c r="U11" s="25">
+      <c r="U11" s="21">
         <v>362</v>
       </c>
-      <c r="V11" s="26">
+      <c r="V11" s="22">
         <v>18200</v>
       </c>
-      <c r="W11" s="26">
+      <c r="W11" s="22">
         <v>69064</v>
       </c>
-      <c r="X11" s="26">
+      <c r="X11" s="22">
         <v>568740</v>
       </c>
-      <c r="Y11" s="26">
+      <c r="Y11" s="22">
         <v>32852</v>
       </c>
-      <c r="Z11" s="26">
+      <c r="Z11" s="22">
         <v>16331</v>
       </c>
-      <c r="AA11" s="26">
+      <c r="AA11" s="22">
         <v>2167</v>
       </c>
-      <c r="AB11" s="26">
+      <c r="AB11" s="22">
         <v>12016359</v>
       </c>
-      <c r="AC11" s="26">
+      <c r="AC11" s="22">
         <v>2312072</v>
       </c>
-      <c r="AD11" s="25">
+      <c r="AD11" s="21">
         <v>639</v>
       </c>
-      <c r="AE11" s="26">
+      <c r="AE11" s="22">
         <v>4143631</v>
       </c>
-      <c r="AF11" s="26">
+      <c r="AF11" s="22">
         <v>12544</v>
       </c>
-      <c r="AG11" s="26">
+      <c r="AG11" s="22">
         <v>3638</v>
       </c>
-      <c r="AH11" s="26">
+      <c r="AH11" s="22">
         <v>1689654</v>
       </c>
-      <c r="AI11" s="26">
+      <c r="AI11" s="22">
         <v>22052201</v>
       </c>
-      <c r="AJ11" s="26">
+      <c r="AJ11" s="22">
         <v>3734826</v>
       </c>
-      <c r="AK11" s="26">
+      <c r="AK11" s="22">
         <v>2267</v>
       </c>
-      <c r="AL11" s="26">
+      <c r="AL11" s="22">
         <v>4403</v>
       </c>
-      <c r="AM11" s="26">
+      <c r="AM11" s="22">
         <v>4122044</v>
       </c>
-      <c r="AN11" s="26">
+      <c r="AN11" s="22">
         <v>1807969</v>
       </c>
-      <c r="AO11" s="26">
+      <c r="AO11" s="22">
         <v>44770</v>
       </c>
-      <c r="AP11" s="26">
+      <c r="AP11" s="22">
         <v>408457</v>
       </c>
-      <c r="AQ11" s="26">
+      <c r="AQ11" s="22">
         <v>3190</v>
       </c>
-      <c r="AR11" s="26">
+      <c r="AR11" s="22">
         <v>17106</v>
       </c>
-      <c r="AS11" s="25">
+      <c r="AS11" s="21">
         <v>131</v>
       </c>
-      <c r="AT11" s="25">
+      <c r="AT11" s="21">
         <v>254</v>
       </c>
-      <c r="AU11" s="25">
+      <c r="AU11" s="21">
         <v>518</v>
       </c>
-      <c r="AV11" s="26">
+      <c r="AV11" s="22">
         <v>10282</v>
       </c>
-      <c r="AW11" s="26">
+      <c r="AW11" s="22">
         <v>10799</v>
       </c>
-      <c r="AX11" s="26">
+      <c r="AX11" s="22">
         <v>3241772</v>
       </c>
-      <c r="AY11" s="26">
+      <c r="AY11" s="22">
         <v>666790</v>
       </c>
-      <c r="AZ11" s="26">
+      <c r="AZ11" s="22">
         <v>7870</v>
       </c>
-      <c r="BA11" s="26">
+      <c r="BA11" s="22">
         <v>45573</v>
       </c>
-      <c r="BB11" s="25">
+      <c r="BB11" s="21">
         <v>115</v>
       </c>
-      <c r="BC11" s="26">
+      <c r="BC11" s="22">
         <v>518534</v>
       </c>
-      <c r="BD11" s="26">
+      <c r="BD11" s="22">
         <v>106581</v>
       </c>
-      <c r="BE11" s="26">
+      <c r="BE11" s="22">
         <v>129114</v>
       </c>
-      <c r="BF11" s="25">
+      <c r="BF11" s="21">
         <v>546</v>
       </c>
-      <c r="BG11" s="26">
+      <c r="BG11" s="22">
         <v>81452</v>
       </c>
-      <c r="BH11" s="26">
+      <c r="BH11" s="22">
         <v>6429107</v>
       </c>
-      <c r="BI11" s="26">
+      <c r="BI11" s="22">
         <v>1632740</v>
       </c>
-      <c r="BJ11" s="25">
+      <c r="BJ11" s="21">
         <v>252</v>
       </c>
-      <c r="BK11" s="26">
+      <c r="BK11" s="22">
         <v>8686</v>
       </c>
-      <c r="BL11" s="26">
+      <c r="BL11" s="22">
         <v>589471</v>
       </c>
-      <c r="BM11" s="26">
+      <c r="BM11" s="22">
         <v>9131</v>
       </c>
-      <c r="BN11" s="26">
+      <c r="BN11" s="22">
         <v>1572626</v>
       </c>
-      <c r="BO11" s="26">
+      <c r="BO11" s="22">
         <v>2357855</v>
       </c>
       <c r="BQ11">
@@ -12101,206 +12099,206 @@
         <v>386537</v>
       </c>
     </row>
-    <row r="12" spans="1:223" x14ac:dyDescent="0.2">
-      <c r="A12" s="25" t="s">
+    <row r="12" spans="1:223" x14ac:dyDescent="0.35">
+      <c r="A12" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="B12" s="26">
+      <c r="B12" s="22">
         <v>42900</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="22">
         <v>1112</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="22">
         <v>1447</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="22">
         <v>5261111</v>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="22">
         <v>2242</v>
       </c>
-      <c r="G12" s="26">
+      <c r="G12" s="22">
         <v>1119</v>
       </c>
-      <c r="H12" s="26">
+      <c r="H12" s="22">
         <v>1263872</v>
       </c>
-      <c r="I12" s="26">
+      <c r="I12" s="22">
         <v>5122853</v>
       </c>
-      <c r="J12" s="25" t="s">
+      <c r="J12" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="K12" s="26">
+      <c r="K12" s="22">
         <v>3809214</v>
       </c>
-      <c r="L12" s="26">
+      <c r="L12" s="22">
         <v>62165</v>
       </c>
-      <c r="M12" s="26">
+      <c r="M12" s="22">
         <v>81990</v>
       </c>
-      <c r="N12" s="26">
+      <c r="N12" s="22">
         <v>1655436</v>
       </c>
-      <c r="O12" s="26">
+      <c r="O12" s="22">
         <v>74003</v>
       </c>
-      <c r="P12" s="26">
+      <c r="P12" s="22">
         <v>5738</v>
       </c>
-      <c r="Q12" s="26">
+      <c r="Q12" s="22">
         <v>227748</v>
       </c>
-      <c r="R12" s="26">
+      <c r="R12" s="22">
         <v>9694</v>
       </c>
-      <c r="S12" s="26">
+      <c r="S12" s="22">
         <v>6467</v>
       </c>
-      <c r="T12" s="26">
+      <c r="T12" s="22">
         <v>103785</v>
       </c>
-      <c r="U12" s="25" t="s">
+      <c r="U12" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="V12" s="26">
+      <c r="V12" s="22">
         <v>21786</v>
       </c>
-      <c r="W12" s="26">
+      <c r="W12" s="22">
         <v>82253</v>
       </c>
-      <c r="X12" s="26">
+      <c r="X12" s="22">
         <v>681150</v>
       </c>
-      <c r="Y12" s="26">
+      <c r="Y12" s="22">
         <v>47723</v>
       </c>
-      <c r="Z12" s="26">
+      <c r="Z12" s="22">
         <v>17768</v>
       </c>
-      <c r="AA12" s="26">
+      <c r="AA12" s="22">
         <v>3221</v>
       </c>
-      <c r="AB12" s="26">
+      <c r="AB12" s="22">
         <v>14361421</v>
       </c>
-      <c r="AC12" s="26">
+      <c r="AC12" s="22">
         <v>2732287</v>
       </c>
-      <c r="AD12" s="25">
+      <c r="AD12" s="21">
         <v>487</v>
       </c>
-      <c r="AE12" s="26">
+      <c r="AE12" s="22">
         <v>5068053</v>
       </c>
-      <c r="AF12" s="26">
+      <c r="AF12" s="22">
         <v>14651</v>
       </c>
-      <c r="AG12" s="26">
+      <c r="AG12" s="22">
         <v>2909</v>
       </c>
-      <c r="AH12" s="26">
+      <c r="AH12" s="22">
         <v>2014857</v>
       </c>
-      <c r="AI12" s="26">
+      <c r="AI12" s="22">
         <v>24404032</v>
       </c>
-      <c r="AJ12" s="26">
+      <c r="AJ12" s="22">
         <v>4775896</v>
       </c>
-      <c r="AK12" s="26">
+      <c r="AK12" s="22">
         <v>1968</v>
       </c>
-      <c r="AL12" s="26">
+      <c r="AL12" s="22">
         <v>4609</v>
       </c>
-      <c r="AM12" s="26">
+      <c r="AM12" s="22">
         <v>5020732</v>
       </c>
-      <c r="AN12" s="26">
+      <c r="AN12" s="22">
         <v>2291453</v>
       </c>
-      <c r="AO12" s="26">
+      <c r="AO12" s="22">
         <v>52316</v>
       </c>
-      <c r="AP12" s="26">
+      <c r="AP12" s="22">
         <v>454349</v>
       </c>
-      <c r="AQ12" s="26">
+      <c r="AQ12" s="22">
         <v>3382</v>
       </c>
-      <c r="AR12" s="26">
+      <c r="AR12" s="22">
         <v>19719</v>
       </c>
-      <c r="AS12" s="25">
+      <c r="AS12" s="21">
         <v>533</v>
       </c>
-      <c r="AT12" s="25">
+      <c r="AT12" s="21">
         <v>169</v>
       </c>
-      <c r="AU12" s="26">
+      <c r="AU12" s="22">
         <v>1447</v>
       </c>
-      <c r="AV12" s="26">
+      <c r="AV12" s="22">
         <v>19630</v>
       </c>
-      <c r="AW12" s="26">
+      <c r="AW12" s="22">
         <v>9584</v>
       </c>
-      <c r="AX12" s="26">
+      <c r="AX12" s="22">
         <v>4063736</v>
       </c>
-      <c r="AY12" s="26">
+      <c r="AY12" s="22">
         <v>856360</v>
       </c>
-      <c r="AZ12" s="26">
+      <c r="AZ12" s="22">
         <v>8960</v>
       </c>
-      <c r="BA12" s="26">
+      <c r="BA12" s="22">
         <v>52663</v>
       </c>
-      <c r="BB12" s="25">
+      <c r="BB12" s="21">
         <v>307</v>
       </c>
-      <c r="BC12" s="26">
+      <c r="BC12" s="22">
         <v>618194</v>
       </c>
-      <c r="BD12" s="26">
+      <c r="BD12" s="22">
         <v>142547</v>
       </c>
-      <c r="BE12" s="26">
+      <c r="BE12" s="22">
         <v>158923</v>
       </c>
-      <c r="BF12" s="25">
+      <c r="BF12" s="21">
         <v>777</v>
       </c>
-      <c r="BG12" s="26">
+      <c r="BG12" s="22">
         <v>87658</v>
       </c>
-      <c r="BH12" s="26">
+      <c r="BH12" s="22">
         <v>8055249</v>
       </c>
-      <c r="BI12" s="26">
+      <c r="BI12" s="22">
         <v>1925429</v>
       </c>
-      <c r="BJ12" s="25">
+      <c r="BJ12" s="21">
         <v>421</v>
       </c>
-      <c r="BK12" s="26">
+      <c r="BK12" s="22">
         <v>11413</v>
       </c>
-      <c r="BL12" s="26">
+      <c r="BL12" s="22">
         <v>703906</v>
       </c>
-      <c r="BM12" s="26">
+      <c r="BM12" s="22">
         <v>13349</v>
       </c>
-      <c r="BN12" s="26">
+      <c r="BN12" s="22">
         <v>1833299</v>
       </c>
-      <c r="BO12" s="26">
+      <c r="BO12" s="22">
         <v>2831762</v>
       </c>
       <c r="BQ12">
@@ -12769,206 +12767,206 @@
         <v>384232</v>
       </c>
     </row>
-    <row r="13" spans="1:223" x14ac:dyDescent="0.2">
-      <c r="A13" s="25" t="s">
+    <row r="13" spans="1:223" x14ac:dyDescent="0.35">
+      <c r="A13" s="21" t="s">
         <v>190</v>
       </c>
-      <c r="B13" s="26">
+      <c r="B13" s="22">
         <v>42041</v>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="22">
         <v>1442</v>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="22">
         <v>1448</v>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="22">
         <v>5052317</v>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="22">
         <v>2258</v>
       </c>
-      <c r="G13" s="25">
+      <c r="G13" s="21">
         <v>452</v>
       </c>
-      <c r="H13" s="26">
+      <c r="H13" s="22">
         <v>1251249</v>
       </c>
-      <c r="I13" s="26">
+      <c r="I13" s="22">
         <v>4708237</v>
       </c>
-      <c r="J13" s="25">
+      <c r="J13" s="21">
         <v>657</v>
       </c>
-      <c r="K13" s="26">
+      <c r="K13" s="22">
         <v>3164839</v>
       </c>
-      <c r="L13" s="26">
+      <c r="L13" s="22">
         <v>65085</v>
       </c>
-      <c r="M13" s="26">
+      <c r="M13" s="22">
         <v>77861</v>
       </c>
-      <c r="N13" s="26">
+      <c r="N13" s="22">
         <v>1566149</v>
       </c>
-      <c r="O13" s="26">
+      <c r="O13" s="22">
         <v>70890</v>
       </c>
-      <c r="P13" s="26">
+      <c r="P13" s="22">
         <v>6769</v>
       </c>
-      <c r="Q13" s="26">
+      <c r="Q13" s="22">
         <v>206836</v>
       </c>
-      <c r="R13" s="26">
+      <c r="R13" s="22">
         <v>11317</v>
       </c>
-      <c r="S13" s="26">
+      <c r="S13" s="22">
         <v>8810</v>
       </c>
-      <c r="T13" s="26">
+      <c r="T13" s="22">
         <v>95968</v>
       </c>
-      <c r="U13" s="25">
+      <c r="U13" s="21">
         <v>206</v>
       </c>
-      <c r="V13" s="26">
+      <c r="V13" s="22">
         <v>19266</v>
       </c>
-      <c r="W13" s="26">
+      <c r="W13" s="22">
         <v>59415</v>
       </c>
-      <c r="X13" s="26">
+      <c r="X13" s="22">
         <v>603034</v>
       </c>
-      <c r="Y13" s="26">
+      <c r="Y13" s="22">
         <v>39875</v>
       </c>
-      <c r="Z13" s="26">
+      <c r="Z13" s="22">
         <v>15900</v>
       </c>
-      <c r="AA13" s="26">
+      <c r="AA13" s="22">
         <v>3243</v>
       </c>
-      <c r="AB13" s="26">
+      <c r="AB13" s="22">
         <v>13998752</v>
       </c>
-      <c r="AC13" s="26">
+      <c r="AC13" s="22">
         <v>2682433</v>
       </c>
-      <c r="AD13" s="25">
+      <c r="AD13" s="21">
         <v>266</v>
       </c>
-      <c r="AE13" s="26">
+      <c r="AE13" s="22">
         <v>4754243</v>
       </c>
-      <c r="AF13" s="26">
+      <c r="AF13" s="22">
         <v>13739</v>
       </c>
-      <c r="AG13" s="26">
+      <c r="AG13" s="22">
         <v>3151</v>
       </c>
-      <c r="AH13" s="26">
+      <c r="AH13" s="22">
         <v>1969788</v>
       </c>
-      <c r="AI13" s="26">
+      <c r="AI13" s="22">
         <v>23368463</v>
       </c>
-      <c r="AJ13" s="26">
+      <c r="AJ13" s="22">
         <v>4444970</v>
       </c>
-      <c r="AK13" s="26">
+      <c r="AK13" s="22">
         <v>1749</v>
       </c>
-      <c r="AL13" s="26">
+      <c r="AL13" s="22">
         <v>4596</v>
       </c>
-      <c r="AM13" s="26">
+      <c r="AM13" s="22">
         <v>4792854</v>
       </c>
-      <c r="AN13" s="26">
+      <c r="AN13" s="22">
         <v>2124058</v>
       </c>
-      <c r="AO13" s="26">
+      <c r="AO13" s="22">
         <v>49362</v>
       </c>
-      <c r="AP13" s="26">
+      <c r="AP13" s="22">
         <v>419998</v>
       </c>
-      <c r="AQ13" s="26">
+      <c r="AQ13" s="22">
         <v>3717</v>
       </c>
-      <c r="AR13" s="26">
+      <c r="AR13" s="22">
         <v>19972</v>
       </c>
-      <c r="AS13" s="25">
+      <c r="AS13" s="21">
         <v>233</v>
       </c>
-      <c r="AT13" s="25">
+      <c r="AT13" s="21">
         <v>254</v>
       </c>
-      <c r="AU13" s="26">
+      <c r="AU13" s="22">
         <v>1493</v>
       </c>
-      <c r="AV13" s="26">
+      <c r="AV13" s="22">
         <v>10532</v>
       </c>
-      <c r="AW13" s="26">
+      <c r="AW13" s="22">
         <v>11703</v>
       </c>
-      <c r="AX13" s="26">
+      <c r="AX13" s="22">
         <v>3556240</v>
       </c>
-      <c r="AY13" s="26">
+      <c r="AY13" s="22">
         <v>762457</v>
       </c>
-      <c r="AZ13" s="26">
+      <c r="AZ13" s="22">
         <v>7305</v>
       </c>
-      <c r="BA13" s="26">
+      <c r="BA13" s="22">
         <v>53220</v>
       </c>
-      <c r="BB13" s="25">
+      <c r="BB13" s="21">
         <v>200</v>
       </c>
-      <c r="BC13" s="26">
+      <c r="BC13" s="22">
         <v>589247</v>
       </c>
-      <c r="BD13" s="26">
+      <c r="BD13" s="22">
         <v>120739</v>
       </c>
-      <c r="BE13" s="26">
+      <c r="BE13" s="22">
         <v>137916</v>
       </c>
-      <c r="BF13" s="25">
+      <c r="BF13" s="21">
         <v>979</v>
       </c>
-      <c r="BG13" s="26">
+      <c r="BG13" s="22">
         <v>83577</v>
       </c>
-      <c r="BH13" s="26">
+      <c r="BH13" s="22">
         <v>7268567</v>
       </c>
-      <c r="BI13" s="26">
+      <c r="BI13" s="22">
         <v>1827128</v>
       </c>
-      <c r="BJ13" s="25">
+      <c r="BJ13" s="21">
         <v>293</v>
       </c>
-      <c r="BK13" s="26">
+      <c r="BK13" s="22">
         <v>14313</v>
       </c>
-      <c r="BL13" s="26">
+      <c r="BL13" s="22">
         <v>621163</v>
       </c>
-      <c r="BM13" s="26">
+      <c r="BM13" s="22">
         <v>11062</v>
       </c>
-      <c r="BN13" s="26">
+      <c r="BN13" s="22">
         <v>1724449</v>
       </c>
-      <c r="BO13" s="26">
+      <c r="BO13" s="22">
         <v>2737457</v>
       </c>
       <c r="BQ13">
@@ -13437,206 +13435,206 @@
         <v>369670</v>
       </c>
     </row>
-    <row r="14" spans="1:223" x14ac:dyDescent="0.2">
-      <c r="A14" s="25" t="s">
+    <row r="14" spans="1:223" x14ac:dyDescent="0.35">
+      <c r="A14" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="B14" s="26">
+      <c r="B14" s="22">
         <v>59066</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="21">
         <v>322</v>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="21">
         <v>546</v>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="22">
         <v>9171839</v>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="22">
         <v>6841</v>
       </c>
-      <c r="G14" s="25">
+      <c r="G14" s="21">
         <v>505</v>
       </c>
-      <c r="H14" s="26">
+      <c r="H14" s="22">
         <v>3216953</v>
       </c>
-      <c r="I14" s="26">
+      <c r="I14" s="22">
         <v>8748948</v>
       </c>
-      <c r="J14" s="25" t="s">
+      <c r="J14" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="K14" s="26">
+      <c r="K14" s="22">
         <v>3545594</v>
       </c>
-      <c r="L14" s="26">
+      <c r="L14" s="22">
         <v>86960</v>
       </c>
-      <c r="M14" s="26">
+      <c r="M14" s="22">
         <v>112434</v>
       </c>
-      <c r="N14" s="26">
+      <c r="N14" s="22">
         <v>2054481</v>
       </c>
-      <c r="O14" s="26">
+      <c r="O14" s="22">
         <v>91375</v>
       </c>
-      <c r="P14" s="26">
+      <c r="P14" s="22">
         <v>11039</v>
       </c>
-      <c r="Q14" s="26">
+      <c r="Q14" s="22">
         <v>361635</v>
       </c>
-      <c r="R14" s="26">
+      <c r="R14" s="22">
         <v>22243</v>
       </c>
-      <c r="S14" s="26">
+      <c r="S14" s="22">
         <v>11874</v>
       </c>
-      <c r="T14" s="26">
+      <c r="T14" s="22">
         <v>191391</v>
       </c>
-      <c r="U14" s="25">
+      <c r="U14" s="21">
         <v>516</v>
       </c>
-      <c r="V14" s="26">
+      <c r="V14" s="22">
         <v>34053</v>
       </c>
-      <c r="W14" s="26">
+      <c r="W14" s="22">
         <v>75432</v>
       </c>
-      <c r="X14" s="26">
+      <c r="X14" s="22">
         <v>659998</v>
       </c>
-      <c r="Y14" s="26">
+      <c r="Y14" s="22">
         <v>54911</v>
       </c>
-      <c r="Z14" s="26">
+      <c r="Z14" s="22">
         <v>15286</v>
       </c>
-      <c r="AA14" s="26">
+      <c r="AA14" s="22">
         <v>4367</v>
       </c>
-      <c r="AB14" s="26">
+      <c r="AB14" s="22">
         <v>25849139</v>
       </c>
-      <c r="AC14" s="26">
+      <c r="AC14" s="22">
         <v>3294494</v>
       </c>
-      <c r="AD14" s="25">
+      <c r="AD14" s="21">
         <v>594</v>
       </c>
-      <c r="AE14" s="26">
+      <c r="AE14" s="22">
         <v>9015386</v>
       </c>
-      <c r="AF14" s="26">
+      <c r="AF14" s="22">
         <v>22556</v>
       </c>
-      <c r="AG14" s="25">
+      <c r="AG14" s="21">
         <v>962</v>
       </c>
-      <c r="AH14" s="26">
+      <c r="AH14" s="22">
         <v>3803232</v>
       </c>
-      <c r="AI14" s="26">
+      <c r="AI14" s="22">
         <v>25774623</v>
       </c>
-      <c r="AJ14" s="26">
+      <c r="AJ14" s="22">
         <v>8611722</v>
       </c>
-      <c r="AK14" s="26">
+      <c r="AK14" s="22">
         <v>2591</v>
       </c>
-      <c r="AL14" s="26">
+      <c r="AL14" s="22">
         <v>7216</v>
       </c>
-      <c r="AM14" s="26">
+      <c r="AM14" s="22">
         <v>8838340</v>
       </c>
-      <c r="AN14" s="26">
+      <c r="AN14" s="22">
         <v>2727461</v>
       </c>
-      <c r="AO14" s="26">
+      <c r="AO14" s="22">
         <v>79905</v>
       </c>
-      <c r="AP14" s="26">
+      <c r="AP14" s="22">
         <v>713239</v>
       </c>
-      <c r="AQ14" s="26">
+      <c r="AQ14" s="22">
         <v>6185</v>
       </c>
-      <c r="AR14" s="26">
+      <c r="AR14" s="22">
         <v>32138</v>
       </c>
-      <c r="AS14" s="25">
+      <c r="AS14" s="21">
         <v>214</v>
       </c>
-      <c r="AT14" s="25">
+      <c r="AT14" s="21">
         <v>168</v>
       </c>
-      <c r="AU14" s="26">
+      <c r="AU14" s="22">
         <v>1581</v>
       </c>
-      <c r="AV14" s="26">
+      <c r="AV14" s="22">
         <v>15085</v>
       </c>
-      <c r="AW14" s="26">
+      <c r="AW14" s="22">
         <v>18235</v>
       </c>
-      <c r="AX14" s="26">
+      <c r="AX14" s="22">
         <v>6605988</v>
       </c>
-      <c r="AY14" s="26">
+      <c r="AY14" s="22">
         <v>2105971</v>
       </c>
-      <c r="AZ14" s="26">
+      <c r="AZ14" s="22">
         <v>9503</v>
       </c>
-      <c r="BA14" s="26">
+      <c r="BA14" s="22">
         <v>70725</v>
       </c>
-      <c r="BB14" s="25" t="s">
+      <c r="BB14" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="BC14" s="26">
+      <c r="BC14" s="22">
         <v>616233</v>
       </c>
-      <c r="BD14" s="26">
+      <c r="BD14" s="22">
         <v>130671</v>
       </c>
-      <c r="BE14" s="26">
+      <c r="BE14" s="22">
         <v>157430</v>
       </c>
-      <c r="BF14" s="25">
+      <c r="BF14" s="21">
         <v>535</v>
       </c>
-      <c r="BG14" s="26">
+      <c r="BG14" s="22">
         <v>85917</v>
       </c>
-      <c r="BH14" s="26">
+      <c r="BH14" s="22">
         <v>14201819</v>
       </c>
-      <c r="BI14" s="26">
+      <c r="BI14" s="22">
         <v>3651956</v>
       </c>
-      <c r="BJ14" s="25">
+      <c r="BJ14" s="21">
         <v>639</v>
       </c>
-      <c r="BK14" s="26">
+      <c r="BK14" s="22">
         <v>13387</v>
       </c>
-      <c r="BL14" s="26">
+      <c r="BL14" s="22">
         <v>1041698</v>
       </c>
-      <c r="BM14" s="26">
+      <c r="BM14" s="22">
         <v>15935</v>
       </c>
-      <c r="BN14" s="26">
+      <c r="BN14" s="22">
         <v>3134293</v>
       </c>
-      <c r="BO14" s="26">
+      <c r="BO14" s="22">
         <v>5146047</v>
       </c>
       <c r="BQ14">
@@ -14105,206 +14103,206 @@
         <v>705169</v>
       </c>
     </row>
-    <row r="15" spans="1:223" x14ac:dyDescent="0.2">
-      <c r="A15" s="25" t="s">
+    <row r="15" spans="1:223" x14ac:dyDescent="0.35">
+      <c r="A15" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="B15" s="26">
+      <c r="B15" s="22">
         <v>51147</v>
       </c>
-      <c r="C15" s="26">
+      <c r="C15" s="22">
         <v>2358</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="22">
         <v>1170</v>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="22">
         <v>7499577</v>
       </c>
-      <c r="F15" s="26">
+      <c r="F15" s="22">
         <v>5623</v>
       </c>
-      <c r="G15" s="26">
+      <c r="G15" s="22">
         <v>1112</v>
       </c>
-      <c r="H15" s="26">
+      <c r="H15" s="22">
         <v>2781597</v>
       </c>
-      <c r="I15" s="26">
+      <c r="I15" s="22">
         <v>7916461</v>
       </c>
-      <c r="J15" s="25">
+      <c r="J15" s="21">
         <v>322</v>
       </c>
-      <c r="K15" s="26">
+      <c r="K15" s="22">
         <v>3733963</v>
       </c>
-      <c r="L15" s="26">
+      <c r="L15" s="22">
         <v>74905</v>
       </c>
-      <c r="M15" s="26">
+      <c r="M15" s="22">
         <v>94457</v>
       </c>
-      <c r="N15" s="26">
+      <c r="N15" s="22">
         <v>1781850</v>
       </c>
-      <c r="O15" s="26">
+      <c r="O15" s="22">
         <v>84383</v>
       </c>
-      <c r="P15" s="26">
+      <c r="P15" s="22">
         <v>6579</v>
       </c>
-      <c r="Q15" s="26">
+      <c r="Q15" s="22">
         <v>311924</v>
       </c>
-      <c r="R15" s="26">
+      <c r="R15" s="22">
         <v>22008</v>
       </c>
-      <c r="S15" s="26">
+      <c r="S15" s="22">
         <v>13907</v>
       </c>
-      <c r="T15" s="26">
+      <c r="T15" s="22">
         <v>160834</v>
       </c>
-      <c r="U15" s="25" t="s">
+      <c r="U15" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="V15" s="26">
+      <c r="V15" s="22">
         <v>30844</v>
       </c>
-      <c r="W15" s="26">
+      <c r="W15" s="22">
         <v>87240</v>
       </c>
-      <c r="X15" s="26">
+      <c r="X15" s="22">
         <v>647078</v>
       </c>
-      <c r="Y15" s="26">
+      <c r="Y15" s="22">
         <v>58661</v>
       </c>
-      <c r="Z15" s="26">
+      <c r="Z15" s="22">
         <v>19832</v>
       </c>
-      <c r="AA15" s="26">
+      <c r="AA15" s="22">
         <v>4364</v>
       </c>
-      <c r="AB15" s="26">
+      <c r="AB15" s="22">
         <v>21873035</v>
       </c>
-      <c r="AC15" s="26">
+      <c r="AC15" s="22">
         <v>2690840</v>
       </c>
-      <c r="AD15" s="25">
+      <c r="AD15" s="21">
         <v>227</v>
       </c>
-      <c r="AE15" s="26">
+      <c r="AE15" s="22">
         <v>8051275</v>
       </c>
-      <c r="AF15" s="26">
+      <c r="AF15" s="22">
         <v>20264</v>
       </c>
-      <c r="AG15" s="26">
+      <c r="AG15" s="22">
         <v>3410</v>
       </c>
-      <c r="AH15" s="26">
+      <c r="AH15" s="22">
         <v>3284946</v>
       </c>
-      <c r="AI15" s="26">
+      <c r="AI15" s="22">
         <v>22997859</v>
       </c>
-      <c r="AJ15" s="26">
+      <c r="AJ15" s="22">
         <v>7052544</v>
       </c>
-      <c r="AK15" s="26">
+      <c r="AK15" s="22">
         <v>4062</v>
       </c>
-      <c r="AL15" s="26">
+      <c r="AL15" s="22">
         <v>8173</v>
       </c>
-      <c r="AM15" s="26">
+      <c r="AM15" s="22">
         <v>7397906</v>
       </c>
-      <c r="AN15" s="26">
+      <c r="AN15" s="22">
         <v>2274942</v>
       </c>
-      <c r="AO15" s="26">
+      <c r="AO15" s="22">
         <v>59000</v>
       </c>
-      <c r="AP15" s="26">
+      <c r="AP15" s="22">
         <v>704621</v>
       </c>
-      <c r="AQ15" s="26">
+      <c r="AQ15" s="22">
         <v>6326</v>
       </c>
-      <c r="AR15" s="26">
+      <c r="AR15" s="22">
         <v>37912</v>
       </c>
-      <c r="AS15" s="25" t="s">
+      <c r="AS15" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="AT15" s="25">
+      <c r="AT15" s="21">
         <v>815</v>
       </c>
-      <c r="AU15" s="26">
+      <c r="AU15" s="22">
         <v>1726</v>
       </c>
-      <c r="AV15" s="26">
+      <c r="AV15" s="22">
         <v>14854</v>
       </c>
-      <c r="AW15" s="26">
+      <c r="AW15" s="22">
         <v>13999</v>
       </c>
-      <c r="AX15" s="26">
+      <c r="AX15" s="22">
         <v>6072096</v>
       </c>
-      <c r="AY15" s="26">
+      <c r="AY15" s="22">
         <v>1908566</v>
       </c>
-      <c r="AZ15" s="26">
+      <c r="AZ15" s="22">
         <v>7682</v>
       </c>
-      <c r="BA15" s="26">
+      <c r="BA15" s="22">
         <v>53609</v>
       </c>
-      <c r="BB15" s="25" t="s">
+      <c r="BB15" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="BC15" s="26">
+      <c r="BC15" s="22">
         <v>523614</v>
       </c>
-      <c r="BD15" s="26">
+      <c r="BD15" s="22">
         <v>124534</v>
       </c>
-      <c r="BE15" s="26">
+      <c r="BE15" s="22">
         <v>139891</v>
       </c>
-      <c r="BF15" s="26">
+      <c r="BF15" s="22">
         <v>1383</v>
       </c>
-      <c r="BG15" s="26">
+      <c r="BG15" s="22">
         <v>79528</v>
       </c>
-      <c r="BH15" s="26">
+      <c r="BH15" s="22">
         <v>12949944</v>
       </c>
-      <c r="BI15" s="26">
+      <c r="BI15" s="22">
         <v>3132520</v>
       </c>
-      <c r="BJ15" s="25">
+      <c r="BJ15" s="21">
         <v>802</v>
       </c>
-      <c r="BK15" s="26">
+      <c r="BK15" s="22">
         <v>14457</v>
       </c>
-      <c r="BL15" s="26">
+      <c r="BL15" s="22">
         <v>974985</v>
       </c>
-      <c r="BM15" s="26">
+      <c r="BM15" s="22">
         <v>14517</v>
       </c>
-      <c r="BN15" s="26">
+      <c r="BN15" s="22">
         <v>2849275</v>
       </c>
-      <c r="BO15" s="26">
+      <c r="BO15" s="22">
         <v>4323412</v>
       </c>
       <c r="BQ15">
@@ -14773,206 +14771,206 @@
         <v>713074</v>
       </c>
     </row>
-    <row r="16" spans="1:223" x14ac:dyDescent="0.2">
-      <c r="A16" s="25" t="s">
+    <row r="16" spans="1:223" x14ac:dyDescent="0.35">
+      <c r="A16" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="B16" s="26">
+      <c r="B16" s="22">
         <v>49434</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="21">
         <v>800</v>
       </c>
-      <c r="D16" s="26">
+      <c r="D16" s="22">
         <v>3021</v>
       </c>
-      <c r="E16" s="26">
+      <c r="E16" s="22">
         <v>7469192</v>
       </c>
-      <c r="F16" s="26">
+      <c r="F16" s="22">
         <v>6655</v>
       </c>
-      <c r="G16" s="25">
+      <c r="G16" s="21">
         <v>987</v>
       </c>
-      <c r="H16" s="26">
+      <c r="H16" s="22">
         <v>2837057</v>
       </c>
-      <c r="I16" s="26">
+      <c r="I16" s="22">
         <v>7910678</v>
       </c>
-      <c r="J16" s="25">
+      <c r="J16" s="21">
         <v>712</v>
       </c>
-      <c r="K16" s="26">
+      <c r="K16" s="22">
         <v>3527433</v>
       </c>
-      <c r="L16" s="26">
+      <c r="L16" s="22">
         <v>68117</v>
       </c>
-      <c r="M16" s="26">
+      <c r="M16" s="22">
         <v>95374</v>
       </c>
-      <c r="N16" s="26">
+      <c r="N16" s="22">
         <v>1975091</v>
       </c>
-      <c r="O16" s="26">
+      <c r="O16" s="22">
         <v>89080</v>
       </c>
-      <c r="P16" s="26">
+      <c r="P16" s="22">
         <v>10066</v>
       </c>
-      <c r="Q16" s="26">
+      <c r="Q16" s="22">
         <v>327039</v>
       </c>
-      <c r="R16" s="26">
+      <c r="R16" s="22">
         <v>18490</v>
       </c>
-      <c r="S16" s="26">
+      <c r="S16" s="22">
         <v>9995</v>
       </c>
-      <c r="T16" s="26">
+      <c r="T16" s="22">
         <v>162435</v>
       </c>
-      <c r="U16" s="25" t="s">
+      <c r="U16" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="V16" s="26">
+      <c r="V16" s="22">
         <v>28346</v>
       </c>
-      <c r="W16" s="26">
+      <c r="W16" s="22">
         <v>91064</v>
       </c>
-      <c r="X16" s="26">
+      <c r="X16" s="22">
         <v>700588</v>
       </c>
-      <c r="Y16" s="26">
+      <c r="Y16" s="22">
         <v>58476</v>
       </c>
-      <c r="Z16" s="26">
+      <c r="Z16" s="22">
         <v>14548</v>
       </c>
-      <c r="AA16" s="26">
+      <c r="AA16" s="22">
         <v>4820</v>
       </c>
-      <c r="AB16" s="26">
+      <c r="AB16" s="22">
         <v>23115286</v>
       </c>
-      <c r="AC16" s="26">
+      <c r="AC16" s="22">
         <v>2700975</v>
       </c>
-      <c r="AD16" s="26">
+      <c r="AD16" s="22">
         <v>1185</v>
       </c>
-      <c r="AE16" s="26">
+      <c r="AE16" s="22">
         <v>7933381</v>
       </c>
-      <c r="AF16" s="26">
+      <c r="AF16" s="22">
         <v>17240</v>
       </c>
-      <c r="AG16" s="26">
+      <c r="AG16" s="22">
         <v>2501</v>
       </c>
-      <c r="AH16" s="26">
+      <c r="AH16" s="22">
         <v>3154673</v>
       </c>
-      <c r="AI16" s="26">
+      <c r="AI16" s="22">
         <v>24671212</v>
       </c>
-      <c r="AJ16" s="26">
+      <c r="AJ16" s="22">
         <v>6991970</v>
       </c>
-      <c r="AK16" s="26">
+      <c r="AK16" s="22">
         <v>3140</v>
       </c>
-      <c r="AL16" s="26">
+      <c r="AL16" s="22">
         <v>5799</v>
       </c>
-      <c r="AM16" s="26">
+      <c r="AM16" s="22">
         <v>7252569</v>
       </c>
-      <c r="AN16" s="26">
+      <c r="AN16" s="22">
         <v>2505612</v>
       </c>
-      <c r="AO16" s="26">
+      <c r="AO16" s="22">
         <v>64831</v>
       </c>
-      <c r="AP16" s="26">
+      <c r="AP16" s="22">
         <v>615695</v>
       </c>
-      <c r="AQ16" s="26">
+      <c r="AQ16" s="22">
         <v>6058</v>
       </c>
-      <c r="AR16" s="26">
+      <c r="AR16" s="22">
         <v>28279</v>
       </c>
-      <c r="AS16" s="25">
+      <c r="AS16" s="21">
         <v>177</v>
       </c>
-      <c r="AT16" s="25">
+      <c r="AT16" s="21">
         <v>466</v>
       </c>
-      <c r="AU16" s="26">
+      <c r="AU16" s="22">
         <v>1871</v>
       </c>
-      <c r="AV16" s="26">
+      <c r="AV16" s="22">
         <v>14497</v>
       </c>
-      <c r="AW16" s="26">
+      <c r="AW16" s="22">
         <v>13588</v>
       </c>
-      <c r="AX16" s="26">
+      <c r="AX16" s="22">
         <v>5601124</v>
       </c>
-      <c r="AY16" s="26">
+      <c r="AY16" s="22">
         <v>1750060</v>
       </c>
-      <c r="AZ16" s="26">
+      <c r="AZ16" s="22">
         <v>7131</v>
       </c>
-      <c r="BA16" s="26">
+      <c r="BA16" s="22">
         <v>60017</v>
       </c>
-      <c r="BB16" s="25" t="s">
+      <c r="BB16" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="BC16" s="26">
+      <c r="BC16" s="22">
         <v>536024</v>
       </c>
-      <c r="BD16" s="26">
+      <c r="BD16" s="22">
         <v>130913</v>
       </c>
-      <c r="BE16" s="26">
+      <c r="BE16" s="22">
         <v>151639</v>
       </c>
-      <c r="BF16" s="26">
+      <c r="BF16" s="22">
         <v>1705</v>
       </c>
-      <c r="BG16" s="26">
+      <c r="BG16" s="22">
         <v>87078</v>
       </c>
-      <c r="BH16" s="26">
+      <c r="BH16" s="22">
         <v>12732682</v>
       </c>
-      <c r="BI16" s="26">
+      <c r="BI16" s="22">
         <v>3048965</v>
       </c>
-      <c r="BJ16" s="25">
+      <c r="BJ16" s="21">
         <v>294</v>
       </c>
-      <c r="BK16" s="26">
+      <c r="BK16" s="22">
         <v>9129</v>
       </c>
-      <c r="BL16" s="26">
+      <c r="BL16" s="22">
         <v>946080</v>
       </c>
-      <c r="BM16" s="26">
+      <c r="BM16" s="22">
         <v>14087</v>
       </c>
-      <c r="BN16" s="26">
+      <c r="BN16" s="22">
         <v>2611136</v>
       </c>
-      <c r="BO16" s="26">
+      <c r="BO16" s="22">
         <v>4199179</v>
       </c>
       <c r="BQ16">
@@ -15441,206 +15439,206 @@
         <v>800243</v>
       </c>
     </row>
-    <row r="17" spans="1:223" x14ac:dyDescent="0.2">
-      <c r="A17" s="25" t="s">
+    <row r="17" spans="1:223" x14ac:dyDescent="0.35">
+      <c r="A17" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="B17" s="26">
+      <c r="B17" s="22">
         <v>49587</v>
       </c>
-      <c r="C17" s="26">
+      <c r="C17" s="22">
         <v>1069</v>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="22">
         <v>1066</v>
       </c>
-      <c r="E17" s="26">
+      <c r="E17" s="22">
         <v>8019872</v>
       </c>
-      <c r="F17" s="26">
+      <c r="F17" s="22">
         <v>7559</v>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="21">
         <v>270</v>
       </c>
-      <c r="H17" s="26">
+      <c r="H17" s="22">
         <v>2885103</v>
       </c>
-      <c r="I17" s="26">
+      <c r="I17" s="22">
         <v>8520522</v>
       </c>
-      <c r="J17" s="25">
+      <c r="J17" s="21">
         <v>331</v>
       </c>
-      <c r="K17" s="26">
+      <c r="K17" s="22">
         <v>3112922</v>
       </c>
-      <c r="L17" s="26">
+      <c r="L17" s="22">
         <v>74670</v>
       </c>
-      <c r="M17" s="26">
+      <c r="M17" s="22">
         <v>92334</v>
       </c>
-      <c r="N17" s="26">
+      <c r="N17" s="22">
         <v>2145293</v>
       </c>
-      <c r="O17" s="26">
+      <c r="O17" s="22">
         <v>75964</v>
       </c>
-      <c r="P17" s="26">
+      <c r="P17" s="22">
         <v>10141</v>
       </c>
-      <c r="Q17" s="26">
+      <c r="Q17" s="22">
         <v>334207</v>
       </c>
-      <c r="R17" s="26">
+      <c r="R17" s="22">
         <v>20316</v>
       </c>
-      <c r="S17" s="26">
+      <c r="S17" s="22">
         <v>5078</v>
       </c>
-      <c r="T17" s="26">
+      <c r="T17" s="22">
         <v>174904</v>
       </c>
-      <c r="U17" s="25">
+      <c r="U17" s="21">
         <v>391</v>
       </c>
-      <c r="V17" s="26">
+      <c r="V17" s="22">
         <v>33996</v>
       </c>
-      <c r="W17" s="26">
+      <c r="W17" s="22">
         <v>66120</v>
       </c>
-      <c r="X17" s="26">
+      <c r="X17" s="22">
         <v>583203</v>
       </c>
-      <c r="Y17" s="26">
+      <c r="Y17" s="22">
         <v>56679</v>
       </c>
-      <c r="Z17" s="26">
+      <c r="Z17" s="22">
         <v>16089</v>
       </c>
-      <c r="AA17" s="26">
+      <c r="AA17" s="22">
         <v>1450</v>
       </c>
-      <c r="AB17" s="26">
+      <c r="AB17" s="22">
         <v>21427051</v>
       </c>
-      <c r="AC17" s="26">
+      <c r="AC17" s="22">
         <v>3084219</v>
       </c>
-      <c r="AD17" s="25">
+      <c r="AD17" s="21">
         <v>456</v>
       </c>
-      <c r="AE17" s="26">
+      <c r="AE17" s="22">
         <v>8718131</v>
       </c>
-      <c r="AF17" s="26">
+      <c r="AF17" s="22">
         <v>19559</v>
       </c>
-      <c r="AG17" s="26">
+      <c r="AG17" s="22">
         <v>1855</v>
       </c>
-      <c r="AH17" s="26">
+      <c r="AH17" s="22">
         <v>3414562</v>
       </c>
-      <c r="AI17" s="26">
+      <c r="AI17" s="22">
         <v>23342632</v>
       </c>
-      <c r="AJ17" s="26">
+      <c r="AJ17" s="22">
         <v>7383590</v>
       </c>
-      <c r="AK17" s="26">
+      <c r="AK17" s="22">
         <v>2564</v>
       </c>
-      <c r="AL17" s="26">
+      <c r="AL17" s="22">
         <v>6101</v>
       </c>
-      <c r="AM17" s="26">
+      <c r="AM17" s="22">
         <v>7672902</v>
       </c>
-      <c r="AN17" s="26">
+      <c r="AN17" s="22">
         <v>2345785</v>
       </c>
-      <c r="AO17" s="26">
+      <c r="AO17" s="22">
         <v>67049</v>
       </c>
-      <c r="AP17" s="26">
+      <c r="AP17" s="22">
         <v>656035</v>
       </c>
-      <c r="AQ17" s="26">
+      <c r="AQ17" s="22">
         <v>4767</v>
       </c>
-      <c r="AR17" s="26">
+      <c r="AR17" s="22">
         <v>32458</v>
       </c>
-      <c r="AS17" s="25">
+      <c r="AS17" s="21">
         <v>280</v>
       </c>
-      <c r="AT17" s="25">
+      <c r="AT17" s="21">
         <v>297</v>
       </c>
-      <c r="AU17" s="25">
+      <c r="AU17" s="21">
         <v>905</v>
       </c>
-      <c r="AV17" s="26">
+      <c r="AV17" s="22">
         <v>11863</v>
       </c>
-      <c r="AW17" s="26">
+      <c r="AW17" s="22">
         <v>14856</v>
       </c>
-      <c r="AX17" s="26">
+      <c r="AX17" s="22">
         <v>6294910</v>
       </c>
-      <c r="AY17" s="26">
+      <c r="AY17" s="22">
         <v>2023940</v>
       </c>
-      <c r="AZ17" s="26">
+      <c r="AZ17" s="22">
         <v>7229</v>
       </c>
-      <c r="BA17" s="26">
+      <c r="BA17" s="22">
         <v>48101</v>
       </c>
-      <c r="BB17" s="25" t="s">
+      <c r="BB17" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="BC17" s="26">
+      <c r="BC17" s="22">
         <v>567338</v>
       </c>
-      <c r="BD17" s="26">
+      <c r="BD17" s="22">
         <v>120777</v>
       </c>
-      <c r="BE17" s="26">
+      <c r="BE17" s="22">
         <v>132772</v>
       </c>
-      <c r="BF17" s="26">
+      <c r="BF17" s="22">
         <v>1588</v>
       </c>
-      <c r="BG17" s="26">
+      <c r="BG17" s="22">
         <v>85278</v>
       </c>
-      <c r="BH17" s="26">
+      <c r="BH17" s="22">
         <v>13703466</v>
       </c>
-      <c r="BI17" s="26">
+      <c r="BI17" s="22">
         <v>3399184</v>
       </c>
-      <c r="BJ17" s="25">
+      <c r="BJ17" s="21">
         <v>252</v>
       </c>
-      <c r="BK17" s="26">
+      <c r="BK17" s="22">
         <v>8212</v>
       </c>
-      <c r="BL17" s="26">
+      <c r="BL17" s="22">
         <v>999732</v>
       </c>
-      <c r="BM17" s="26">
+      <c r="BM17" s="22">
         <v>10694</v>
       </c>
-      <c r="BN17" s="26">
+      <c r="BN17" s="22">
         <v>2905786</v>
       </c>
-      <c r="BO17" s="26">
+      <c r="BO17" s="22">
         <v>4535818</v>
       </c>
       <c r="BQ17">
@@ -16109,206 +16107,206 @@
         <v>691656</v>
       </c>
     </row>
-    <row r="18" spans="1:223" x14ac:dyDescent="0.2">
-      <c r="A18" s="25" t="s">
+    <row r="18" spans="1:223" x14ac:dyDescent="0.35">
+      <c r="A18" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="B18" s="26">
+      <c r="B18" s="22">
         <v>55822</v>
       </c>
-      <c r="C18" s="26">
+      <c r="C18" s="22">
         <v>1892</v>
       </c>
-      <c r="D18" s="25">
+      <c r="D18" s="21">
         <v>559</v>
       </c>
-      <c r="E18" s="26">
+      <c r="E18" s="22">
         <v>6940400</v>
       </c>
-      <c r="F18" s="26">
+      <c r="F18" s="22">
         <v>4369</v>
       </c>
-      <c r="G18" s="25">
+      <c r="G18" s="21">
         <v>259</v>
       </c>
-      <c r="H18" s="26">
+      <c r="H18" s="22">
         <v>2608434</v>
       </c>
-      <c r="I18" s="26">
+      <c r="I18" s="22">
         <v>7575221</v>
       </c>
-      <c r="J18" s="25" t="s">
+      <c r="J18" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="K18" s="26">
+      <c r="K18" s="22">
         <v>3333080</v>
       </c>
-      <c r="L18" s="26">
+      <c r="L18" s="22">
         <v>66885</v>
       </c>
-      <c r="M18" s="26">
+      <c r="M18" s="22">
         <v>90017</v>
       </c>
-      <c r="N18" s="26">
+      <c r="N18" s="22">
         <v>2054913</v>
       </c>
-      <c r="O18" s="26">
+      <c r="O18" s="22">
         <v>85408</v>
       </c>
-      <c r="P18" s="26">
+      <c r="P18" s="22">
         <v>8873</v>
       </c>
-      <c r="Q18" s="26">
+      <c r="Q18" s="22">
         <v>305793</v>
       </c>
-      <c r="R18" s="26">
+      <c r="R18" s="22">
         <v>17274</v>
       </c>
-      <c r="S18" s="26">
+      <c r="S18" s="22">
         <v>1796</v>
       </c>
-      <c r="T18" s="26">
+      <c r="T18" s="22">
         <v>155087</v>
       </c>
-      <c r="U18" s="25" t="s">
+      <c r="U18" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="V18" s="26">
+      <c r="V18" s="22">
         <v>26200</v>
       </c>
-      <c r="W18" s="26">
+      <c r="W18" s="22">
         <v>71169</v>
       </c>
-      <c r="X18" s="26">
+      <c r="X18" s="22">
         <v>649071</v>
       </c>
-      <c r="Y18" s="26">
+      <c r="Y18" s="22">
         <v>53426</v>
       </c>
-      <c r="Z18" s="26">
+      <c r="Z18" s="22">
         <v>18786</v>
       </c>
-      <c r="AA18" s="26">
+      <c r="AA18" s="22">
         <v>3017</v>
       </c>
-      <c r="AB18" s="26">
+      <c r="AB18" s="22">
         <v>21409855</v>
       </c>
-      <c r="AC18" s="26">
+      <c r="AC18" s="22">
         <v>2705147</v>
       </c>
-      <c r="AD18" s="25">
+      <c r="AD18" s="21">
         <v>397</v>
       </c>
-      <c r="AE18" s="26">
+      <c r="AE18" s="22">
         <v>7656229</v>
       </c>
-      <c r="AF18" s="26">
+      <c r="AF18" s="22">
         <v>16612</v>
       </c>
-      <c r="AG18" s="25">
+      <c r="AG18" s="21">
         <v>915</v>
       </c>
-      <c r="AH18" s="26">
+      <c r="AH18" s="22">
         <v>3111221</v>
       </c>
-      <c r="AI18" s="26">
+      <c r="AI18" s="22">
         <v>24607797</v>
       </c>
-      <c r="AJ18" s="26">
+      <c r="AJ18" s="22">
         <v>6716291</v>
       </c>
-      <c r="AK18" s="26">
+      <c r="AK18" s="22">
         <v>2403</v>
       </c>
-      <c r="AL18" s="26">
+      <c r="AL18" s="22">
         <v>8442</v>
       </c>
-      <c r="AM18" s="26">
+      <c r="AM18" s="22">
         <v>6965903</v>
       </c>
-      <c r="AN18" s="26">
+      <c r="AN18" s="22">
         <v>2376626</v>
       </c>
-      <c r="AO18" s="26">
+      <c r="AO18" s="22">
         <v>53303</v>
       </c>
-      <c r="AP18" s="26">
+      <c r="AP18" s="22">
         <v>525545</v>
       </c>
-      <c r="AQ18" s="26">
+      <c r="AQ18" s="22">
         <v>6349</v>
       </c>
-      <c r="AR18" s="26">
+      <c r="AR18" s="22">
         <v>28803</v>
       </c>
-      <c r="AS18" s="25">
+      <c r="AS18" s="21">
         <v>199</v>
       </c>
-      <c r="AT18" s="25">
+      <c r="AT18" s="21">
         <v>241</v>
       </c>
-      <c r="AU18" s="26">
+      <c r="AU18" s="22">
         <v>1956</v>
       </c>
-      <c r="AV18" s="26">
+      <c r="AV18" s="22">
         <v>10695</v>
       </c>
-      <c r="AW18" s="26">
+      <c r="AW18" s="22">
         <v>12525</v>
       </c>
-      <c r="AX18" s="26">
+      <c r="AX18" s="22">
         <v>5302694</v>
       </c>
-      <c r="AY18" s="26">
+      <c r="AY18" s="22">
         <v>1806681</v>
       </c>
-      <c r="AZ18" s="26">
+      <c r="AZ18" s="22">
         <v>5861</v>
       </c>
-      <c r="BA18" s="26">
+      <c r="BA18" s="22">
         <v>50492</v>
       </c>
-      <c r="BB18" s="25" t="s">
+      <c r="BB18" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="BC18" s="26">
+      <c r="BC18" s="22">
         <v>530199</v>
       </c>
-      <c r="BD18" s="26">
+      <c r="BD18" s="22">
         <v>121393</v>
       </c>
-      <c r="BE18" s="26">
+      <c r="BE18" s="22">
         <v>150995</v>
       </c>
-      <c r="BF18" s="26">
+      <c r="BF18" s="22">
         <v>1538</v>
       </c>
-      <c r="BG18" s="26">
+      <c r="BG18" s="22">
         <v>85062</v>
       </c>
-      <c r="BH18" s="26">
+      <c r="BH18" s="22">
         <v>12775504</v>
       </c>
-      <c r="BI18" s="26">
+      <c r="BI18" s="22">
         <v>2922465</v>
       </c>
-      <c r="BJ18" s="26">
+      <c r="BJ18" s="22">
         <v>1139</v>
       </c>
-      <c r="BK18" s="26">
+      <c r="BK18" s="22">
         <v>10003</v>
       </c>
-      <c r="BL18" s="26">
+      <c r="BL18" s="22">
         <v>883209</v>
       </c>
-      <c r="BM18" s="26">
+      <c r="BM18" s="22">
         <v>10065</v>
       </c>
-      <c r="BN18" s="26">
+      <c r="BN18" s="22">
         <v>2520851</v>
       </c>
-      <c r="BO18" s="26">
+      <c r="BO18" s="22">
         <v>4062989</v>
       </c>
       <c r="BQ18">
@@ -16777,206 +16775,206 @@
         <v>719682</v>
       </c>
     </row>
-    <row r="19" spans="1:223" x14ac:dyDescent="0.2">
-      <c r="A19" s="25" t="s">
+    <row r="19" spans="1:223" x14ac:dyDescent="0.35">
+      <c r="A19" s="21" t="s">
         <v>196</v>
       </c>
-      <c r="B19" s="26">
+      <c r="B19" s="22">
         <v>36938</v>
       </c>
-      <c r="C19" s="25">
+      <c r="C19" s="21">
         <v>287</v>
       </c>
-      <c r="D19" s="25">
+      <c r="D19" s="21">
         <v>591</v>
       </c>
-      <c r="E19" s="26">
+      <c r="E19" s="22">
         <v>6447593</v>
       </c>
-      <c r="F19" s="26">
+      <c r="F19" s="22">
         <v>3501</v>
       </c>
-      <c r="G19" s="25">
+      <c r="G19" s="21">
         <v>338</v>
       </c>
-      <c r="H19" s="26">
+      <c r="H19" s="22">
         <v>2132281</v>
       </c>
-      <c r="I19" s="26">
+      <c r="I19" s="22">
         <v>7037201</v>
       </c>
-      <c r="J19" s="25" t="s">
+      <c r="J19" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="K19" s="26">
+      <c r="K19" s="22">
         <v>3285980</v>
       </c>
-      <c r="L19" s="26">
+      <c r="L19" s="22">
         <v>67434</v>
       </c>
-      <c r="M19" s="26">
+      <c r="M19" s="22">
         <v>78732</v>
       </c>
-      <c r="N19" s="26">
+      <c r="N19" s="22">
         <v>1723093</v>
       </c>
-      <c r="O19" s="26">
+      <c r="O19" s="22">
         <v>62365</v>
       </c>
-      <c r="P19" s="26">
+      <c r="P19" s="22">
         <v>8479</v>
       </c>
-      <c r="Q19" s="26">
+      <c r="Q19" s="22">
         <v>284023</v>
       </c>
-      <c r="R19" s="26">
+      <c r="R19" s="22">
         <v>16706</v>
       </c>
-      <c r="S19" s="26">
+      <c r="S19" s="22">
         <v>4306</v>
       </c>
-      <c r="T19" s="26">
+      <c r="T19" s="22">
         <v>141297</v>
       </c>
-      <c r="U19" s="25" t="s">
+      <c r="U19" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="V19" s="26">
+      <c r="V19" s="22">
         <v>28477</v>
       </c>
-      <c r="W19" s="26">
+      <c r="W19" s="22">
         <v>73680</v>
       </c>
-      <c r="X19" s="26">
+      <c r="X19" s="22">
         <v>580168</v>
       </c>
-      <c r="Y19" s="26">
+      <c r="Y19" s="22">
         <v>40091</v>
       </c>
-      <c r="Z19" s="26">
+      <c r="Z19" s="22">
         <v>16797</v>
       </c>
-      <c r="AA19" s="26">
+      <c r="AA19" s="22">
         <v>1161</v>
       </c>
-      <c r="AB19" s="26">
+      <c r="AB19" s="22">
         <v>17347824</v>
       </c>
-      <c r="AC19" s="26">
+      <c r="AC19" s="22">
         <v>2547270</v>
       </c>
-      <c r="AD19" s="25">
+      <c r="AD19" s="21">
         <v>608</v>
       </c>
-      <c r="AE19" s="26">
+      <c r="AE19" s="22">
         <v>7092865</v>
       </c>
-      <c r="AF19" s="26">
+      <c r="AF19" s="22">
         <v>17111</v>
       </c>
-      <c r="AG19" s="26">
+      <c r="AG19" s="22">
         <v>1491</v>
       </c>
-      <c r="AH19" s="26">
+      <c r="AH19" s="22">
         <v>2692634</v>
       </c>
-      <c r="AI19" s="26">
+      <c r="AI19" s="22">
         <v>20542623</v>
       </c>
-      <c r="AJ19" s="26">
+      <c r="AJ19" s="22">
         <v>6040903</v>
       </c>
-      <c r="AK19" s="26">
+      <c r="AK19" s="22">
         <v>3287</v>
       </c>
-      <c r="AL19" s="26">
+      <c r="AL19" s="22">
         <v>6299</v>
       </c>
-      <c r="AM19" s="26">
+      <c r="AM19" s="22">
         <v>6190345</v>
       </c>
-      <c r="AN19" s="26">
+      <c r="AN19" s="22">
         <v>2090381</v>
       </c>
-      <c r="AO19" s="26">
+      <c r="AO19" s="22">
         <v>52328</v>
       </c>
-      <c r="AP19" s="26">
+      <c r="AP19" s="22">
         <v>608777</v>
       </c>
-      <c r="AQ19" s="26">
+      <c r="AQ19" s="22">
         <v>5009</v>
       </c>
-      <c r="AR19" s="26">
+      <c r="AR19" s="22">
         <v>26265</v>
       </c>
-      <c r="AS19" s="25">
+      <c r="AS19" s="21">
         <v>150</v>
       </c>
-      <c r="AT19" s="25">
+      <c r="AT19" s="21">
         <v>242</v>
       </c>
-      <c r="AU19" s="26">
+      <c r="AU19" s="22">
         <v>1227</v>
       </c>
-      <c r="AV19" s="26">
+      <c r="AV19" s="22">
         <v>11622</v>
       </c>
-      <c r="AW19" s="26">
+      <c r="AW19" s="22">
         <v>12872</v>
       </c>
-      <c r="AX19" s="26">
+      <c r="AX19" s="22">
         <v>5373557</v>
       </c>
-      <c r="AY19" s="26">
+      <c r="AY19" s="22">
         <v>1607780</v>
       </c>
-      <c r="AZ19" s="26">
+      <c r="AZ19" s="22">
         <v>4828</v>
       </c>
-      <c r="BA19" s="26">
+      <c r="BA19" s="22">
         <v>38418</v>
       </c>
-      <c r="BB19" s="25">
+      <c r="BB19" s="21">
         <v>184</v>
       </c>
-      <c r="BC19" s="26">
+      <c r="BC19" s="22">
         <v>494962</v>
       </c>
-      <c r="BD19" s="26">
+      <c r="BD19" s="22">
         <v>110182</v>
       </c>
-      <c r="BE19" s="26">
+      <c r="BE19" s="22">
         <v>133199</v>
       </c>
-      <c r="BF19" s="25">
+      <c r="BF19" s="21">
         <v>654</v>
       </c>
-      <c r="BG19" s="26">
+      <c r="BG19" s="22">
         <v>73973</v>
       </c>
-      <c r="BH19" s="26">
+      <c r="BH19" s="22">
         <v>11989360</v>
       </c>
-      <c r="BI19" s="26">
+      <c r="BI19" s="22">
         <v>2575527</v>
       </c>
-      <c r="BJ19" s="25">
+      <c r="BJ19" s="21">
         <v>637</v>
       </c>
-      <c r="BK19" s="26">
+      <c r="BK19" s="22">
         <v>7069</v>
       </c>
-      <c r="BL19" s="26">
+      <c r="BL19" s="22">
         <v>934386</v>
       </c>
-      <c r="BM19" s="26">
+      <c r="BM19" s="22">
         <v>14326</v>
       </c>
-      <c r="BN19" s="26">
+      <c r="BN19" s="22">
         <v>2571340</v>
       </c>
-      <c r="BO19" s="26">
+      <c r="BO19" s="22">
         <v>3625245</v>
       </c>
       <c r="BQ19">
@@ -17445,7 +17443,7 @@
         <v>678161</v>
       </c>
     </row>
-    <row r="24" spans="1:223" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:223" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>14</v>
       </c>
@@ -17453,7 +17451,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:223" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:223" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>352</v>
       </c>
@@ -17464,7 +17462,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="27" spans="1:223" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:223" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>353</v>
       </c>
@@ -17475,7 +17473,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="28" spans="1:223" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:223" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>354</v>
       </c>
@@ -17486,7 +17484,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:223" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:223" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>355</v>
       </c>
@@ -17497,7 +17495,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="30" spans="1:223" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:223" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>356</v>
       </c>
@@ -17508,7 +17506,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:223" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:223" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>357</v>
       </c>
@@ -17519,7 +17517,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:223" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:223" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>358</v>
       </c>
@@ -17530,7 +17528,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>359</v>
       </c>
@@ -17547,9 +17545,9 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.5" customWidth="1"/>
     <col min="2" max="2" width="20.1640625" customWidth="1"/>
@@ -17557,7 +17555,7 @@
     <col min="4" max="4" width="18.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -17571,7 +17569,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>100</v>
       </c>
@@ -17585,7 +17583,7 @@
         <v>67.924528300000006</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>100</v>
       </c>
@@ -17599,7 +17597,7 @@
         <v>59.388646289999997</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>100</v>
       </c>
@@ -17613,7 +17611,7 @@
         <v>54.629629629999997</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>13</v>
       </c>
@@ -17624,7 +17622,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C7" t="s">
         <v>12</v>
       </c>
@@ -17638,34 +17636,34 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:O5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27" t="s">
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23" t="s">
         <v>79</v>
       </c>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27" t="s">
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27" t="s">
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
       <c r="N1" s="3" t="s">
         <v>14</v>
       </c>
@@ -17673,8 +17671,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A2" s="22">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A2" s="19">
         <v>0</v>
       </c>
       <c r="B2" s="1">
@@ -17714,8 +17712,8 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A3" s="22">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A3" s="19">
         <v>10</v>
       </c>
       <c r="B3" s="1">
@@ -17761,8 +17759,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A4" s="22">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A4" s="19">
         <v>5</v>
       </c>
       <c r="B4" s="1">
@@ -17808,8 +17806,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A5" s="22">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A5" s="19">
         <v>2</v>
       </c>
       <c r="B5" s="1">
@@ -17867,30 +17865,30 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:J13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" s="21">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" s="18">
         <v>23</v>
       </c>
       <c r="B5" s="1">
@@ -17912,8 +17910,8 @@
         <v>11.84</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="21">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" s="18">
         <v>25</v>
       </c>
       <c r="B6" s="1">
@@ -17935,8 +17933,8 @@
         <v>47.526600000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" s="21">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" s="18">
         <v>28</v>
       </c>
       <c r="B7" s="1">
@@ -17958,18 +17956,18 @@
         <v>67.830699999999993</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11" s="21">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11" s="18">
         <v>23</v>
       </c>
       <c r="B11" s="1">
@@ -17997,8 +17995,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A12" s="21">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" s="18">
         <v>25</v>
       </c>
       <c r="B12" s="1">
@@ -18026,8 +18024,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A13" s="21">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" s="18">
         <v>28</v>
       </c>
       <c r="B13" s="1">
